--- a/outputs/57232.xlsx
+++ b/outputs/57232.xlsx
@@ -340,44 +340,48 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -667,5169 +671,5169 @@
   <dimension ref="A1:H191"/>
   <sheetFormatPr defaultColWidth="11.4296875" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1" t="n">
+      <c r="E2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H2" s="6" t="n">
-        <f aca="false" t="array" ref="H2:H2">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B2)*(Volume!$B$3:$B$68=E2),0), MATCH(D2,Volume!$D$2:$F$2,0))</f>
+      <c r="H2" s="7" t="n">
+        <f aca="false" t="array" ref="H2:H2">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B2)*(Volume!$B$3:$B$68=$E2),0),MATCH($D2,Volume!$D$2:$F$2,0))</f>
         <v>42.25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="1" t="n">
+      <c r="E3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H3" s="6" t="n">
-        <f aca="false" t="array" ref="H3:H3">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B3)*(Volume!$B$3:$B$68=E3),0), MATCH(D3,Volume!$D$2:$F$2,0))</f>
+      <c r="H3" s="7" t="n">
+        <f aca="false" t="array" ref="H3:H3">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B3)*(Volume!$B$3:$B$68=$E3),0),MATCH($D3,Volume!$D$2:$F$2,0))</f>
         <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="1" t="n">
+      <c r="E4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="H4" s="6" t="n">
-        <f aca="false" t="array" ref="H4:H4">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B4)*(Volume!$B$3:$B$68=E4),0), MATCH(D4,Volume!$D$2:$F$2,0))</f>
+      <c r="H4" s="7" t="n">
+        <f aca="false" t="array" ref="H4:H4">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B4)*(Volume!$B$3:$B$68=$E4),0),MATCH($D4,Volume!$D$2:$F$2,0))</f>
         <v>8.5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="1" t="n">
+      <c r="E5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="H5" s="6" t="n">
-        <f aca="false" t="array" ref="H5:H5">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B5)*(Volume!$B$3:$B$68=E5),0), MATCH(D5,Volume!$D$2:$F$2,0))</f>
+      <c r="H5" s="7" t="n">
+        <f aca="false" t="array" ref="H5:H5">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B5)*(Volume!$B$3:$B$68=$E5),0),MATCH($D5,Volume!$D$2:$F$2,0))</f>
         <v>8.5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="1" t="n">
+      <c r="E6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H6" s="6" t="n">
-        <f aca="false" t="array" ref="H6:H6">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B6)*(Volume!$B$3:$B$68=E6),0), MATCH(D6,Volume!$D$2:$F$2,0))</f>
+      <c r="H6" s="7" t="n">
+        <f aca="false" t="array" ref="H6:H6">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B6)*(Volume!$B$3:$B$68=$E6),0),MATCH($D6,Volume!$D$2:$F$2,0))</f>
         <v>8.75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="1" t="n">
+      <c r="E7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H7" s="6" t="n">
-        <f aca="false" t="array" ref="H7:H7">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B7)*(Volume!$B$3:$B$68=E7),0), MATCH(D7,Volume!$D$2:$F$2,0))</f>
+      <c r="H7" s="7" t="n">
+        <f aca="false" t="array" ref="H7:H7">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B7)*(Volume!$B$3:$B$68=$E7),0),MATCH($D7,Volume!$D$2:$F$2,0))</f>
         <v>2.75</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="1" t="n">
+      <c r="E8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H8" s="6" t="n">
-        <f aca="false" t="array" ref="H8:H8">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B8)*(Volume!$B$3:$B$68=E8),0), MATCH(D8,Volume!$D$2:$F$2,0))</f>
+      <c r="H8" s="7" t="n">
+        <f aca="false" t="array" ref="H8:H8">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B8)*(Volume!$B$3:$B$68=$E8),0),MATCH($D8,Volume!$D$2:$F$2,0))</f>
         <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="1" t="n">
+      <c r="E9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H9" s="6" t="n">
-        <f aca="false" t="array" ref="H9:H9">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B9)*(Volume!$B$3:$B$68=E9),0), MATCH(D9,Volume!$D$2:$F$2,0))</f>
+      <c r="H9" s="7" t="n">
+        <f aca="false" t="array" ref="H9:H9">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B9)*(Volume!$B$3:$B$68=$E9),0),MATCH($D9,Volume!$D$2:$F$2,0))</f>
         <v>2.25</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="1" t="n">
+      <c r="E10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H10" s="6" t="n">
-        <f aca="false" t="array" ref="H10:H10">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B10)*(Volume!$B$3:$B$68=E10),0), MATCH(D10,Volume!$D$2:$F$2,0))</f>
+      <c r="H10" s="7" t="n">
+        <f aca="false" t="array" ref="H10:H10">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B10)*(Volume!$B$3:$B$68=$E10),0),MATCH($D10,Volume!$D$2:$F$2,0))</f>
         <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="1" t="n">
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H11" s="6" t="n">
-        <f aca="false" t="array" ref="H11:H11">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B11)*(Volume!$B$3:$B$68=E11),0), MATCH(D11,Volume!$D$2:$F$2,0))</f>
+      <c r="H11" s="7" t="n">
+        <f aca="false" t="array" ref="H11:H11">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B11)*(Volume!$B$3:$B$68=$E11),0),MATCH($D11,Volume!$D$2:$F$2,0))</f>
         <v>1.75</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="1" t="n">
+      <c r="E12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H12" s="6" t="n">
-        <f aca="false" t="array" ref="H12:H12">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B12)*(Volume!$B$3:$B$68=E12),0), MATCH(D12,Volume!$D$2:$F$2,0))</f>
+      <c r="H12" s="7" t="n">
+        <f aca="false" t="array" ref="H12:H12">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B12)*(Volume!$B$3:$B$68=$E12),0),MATCH($D12,Volume!$D$2:$F$2,0))</f>
         <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="1" t="n">
+      <c r="E13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>575</v>
       </c>
-      <c r="H13" s="6" t="n">
-        <f aca="false" t="array" ref="H13:H13">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B13)*(Volume!$B$3:$B$68=E13),0), MATCH(D13,Volume!$D$2:$F$2,0))</f>
+      <c r="H13" s="7" t="n">
+        <f aca="false" t="array" ref="H13:H13">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B13)*(Volume!$B$3:$B$68=$E13),0),MATCH($D13,Volume!$D$2:$F$2,0))</f>
         <v>1.75</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="1" t="n">
+      <c r="E14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="H14" s="6" t="n">
-        <f aca="false" t="array" ref="H14:H14">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B14)*(Volume!$B$3:$B$68=E14),0), MATCH(D14,Volume!$D$2:$F$2,0))</f>
+      <c r="H14" s="7" t="n">
+        <f aca="false" t="array" ref="H14:H14">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B14)*(Volume!$B$3:$B$68=$E14),0),MATCH($D14,Volume!$D$2:$F$2,0))</f>
         <v>1.25</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="1" t="n">
+      <c r="E15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H15" s="6" t="n">
-        <f aca="false" t="array" ref="H15:H15">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B15)*(Volume!$B$3:$B$68=E15),0), MATCH(D15,Volume!$D$2:$F$2,0))</f>
+      <c r="H15" s="7" t="n">
+        <f aca="false" t="array" ref="H15:H15">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B15)*(Volume!$B$3:$B$68=$E15),0),MATCH($D15,Volume!$D$2:$F$2,0))</f>
         <v>1.25</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="1" t="n">
+      <c r="E16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H16" s="6" t="n">
-        <f aca="false" t="array" ref="H16:H16">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B16)*(Volume!$B$3:$B$68=E16),0), MATCH(D16,Volume!$D$2:$F$2,0))</f>
+      <c r="H16" s="7" t="n">
+        <f aca="false" t="array" ref="H16:H16">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B16)*(Volume!$B$3:$B$68=$E16),0),MATCH($D16,Volume!$D$2:$F$2,0))</f>
         <v>1.5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="1" t="n">
+      <c r="E17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="H17" s="6" t="n">
-        <f aca="false" t="array" ref="H17:H17">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B17)*(Volume!$B$3:$B$68=E17),0), MATCH(D17,Volume!$D$2:$F$2,0))</f>
+      <c r="H17" s="7" t="n">
+        <f aca="false" t="array" ref="H17:H17">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B17)*(Volume!$B$3:$B$68=$E17),0),MATCH($D17,Volume!$D$2:$F$2,0))</f>
         <v>1.25</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="1" t="n">
+      <c r="E18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H18" s="6" t="n">
-        <f aca="false" t="array" ref="H18:H18">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B18)*(Volume!$B$3:$B$68=E18),0), MATCH(D18,Volume!$D$2:$F$2,0))</f>
+      <c r="H18" s="7" t="n">
+        <f aca="false" t="array" ref="H18:H18">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B18)*(Volume!$B$3:$B$68=$E18),0),MATCH($D18,Volume!$D$2:$F$2,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="1" t="n">
+      <c r="E19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H19" s="6" t="n">
-        <f aca="false" t="array" ref="H19:H19">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B19)*(Volume!$B$3:$B$68=E19),0), MATCH(D19,Volume!$D$2:$F$2,0))</f>
+      <c r="H19" s="7" t="n">
+        <f aca="false" t="array" ref="H19:H19">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B19)*(Volume!$B$3:$B$68=$E19),0),MATCH($D19,Volume!$D$2:$F$2,0))</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="1" t="n">
+      <c r="E20" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H20" s="6" t="n">
-        <f aca="false" t="array" ref="H20:H20">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B20)*(Volume!$B$3:$B$68=E20),0), MATCH(D20,Volume!$D$2:$F$2,0))</f>
+      <c r="H20" s="7" t="n">
+        <f aca="false" t="array" ref="H20:H20">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B20)*(Volume!$B$3:$B$68=$E20),0),MATCH($D20,Volume!$D$2:$F$2,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="1" t="n">
+      <c r="E21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H21" s="6" t="n">
-        <f aca="false" t="array" ref="H21:H21">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B21)*(Volume!$B$3:$B$68=E21),0), MATCH(D21,Volume!$D$2:$F$2,0))</f>
+      <c r="H21" s="7" t="n">
+        <f aca="false" t="array" ref="H21:H21">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B21)*(Volume!$B$3:$B$68=$E21),0),MATCH($D21,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="1" t="n">
+      <c r="E22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H22" s="6" t="n">
-        <f aca="false" t="array" ref="H22:H22">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B22)*(Volume!$B$3:$B$68=E22),0), MATCH(D22,Volume!$D$2:$F$2,0))</f>
+      <c r="H22" s="7" t="n">
+        <f aca="false" t="array" ref="H22:H22">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B22)*(Volume!$B$3:$B$68=$E22),0),MATCH($D22,Volume!$D$2:$F$2,0))</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="1" t="n">
+      <c r="E23" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H23" s="6" t="n">
-        <f aca="false" t="array" ref="H23:H23">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B23)*(Volume!$B$3:$B$68=E23),0), MATCH(D23,Volume!$D$2:$F$2,0))</f>
+      <c r="H23" s="7" t="n">
+        <f aca="false" t="array" ref="H23:H23">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B23)*(Volume!$B$3:$B$68=$E23),0),MATCH($D23,Volume!$D$2:$F$2,0))</f>
         <v>60</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="1" t="n">
+      <c r="E24" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H24" s="6" t="n">
-        <f aca="false" t="array" ref="H24:H24">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B24)*(Volume!$B$3:$B$68=E24),0), MATCH(D24,Volume!$D$2:$F$2,0))</f>
+      <c r="H24" s="7" t="n">
+        <f aca="false" t="array" ref="H24:H24">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B24)*(Volume!$B$3:$B$68=$E24),0),MATCH($D24,Volume!$D$2:$F$2,0))</f>
         <v>33</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="1" t="n">
+      <c r="E25" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H25" s="6" t="n">
-        <f aca="false" t="array" ref="H25:H25">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B25)*(Volume!$B$3:$B$68=E25),0), MATCH(D25,Volume!$D$2:$F$2,0))</f>
+      <c r="H25" s="7" t="n">
+        <f aca="false" t="array" ref="H25:H25">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B25)*(Volume!$B$3:$B$68=$E25),0),MATCH($D25,Volume!$D$2:$F$2,0))</f>
         <v>9</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="1" t="n">
+      <c r="E26" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H26" s="6" t="n">
-        <f aca="false" t="array" ref="H26:H26">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B26)*(Volume!$B$3:$B$68=E26),0), MATCH(D26,Volume!$D$2:$F$2,0))</f>
+      <c r="H26" s="7" t="n">
+        <f aca="false" t="array" ref="H26:H26">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B26)*(Volume!$B$3:$B$68=$E26),0),MATCH($D26,Volume!$D$2:$F$2,0))</f>
         <v>2.25</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="1" t="n">
+      <c r="E27" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H27" s="6" t="n">
-        <f aca="false" t="array" ref="H27:H27">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B27)*(Volume!$B$3:$B$68=E27),0), MATCH(D27,Volume!$D$2:$F$2,0))</f>
+      <c r="H27" s="7" t="n">
+        <f aca="false" t="array" ref="H27:H27">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B27)*(Volume!$B$3:$B$68=$E27),0),MATCH($D27,Volume!$D$2:$F$2,0))</f>
         <v>8.5</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="1" t="n">
+      <c r="E28" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H28" s="6" t="n">
-        <f aca="false" t="array" ref="H28:H28">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B28)*(Volume!$B$3:$B$68=E28),0), MATCH(D28,Volume!$D$2:$F$2,0))</f>
+      <c r="H28" s="7" t="n">
+        <f aca="false" t="array" ref="H28:H28">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B28)*(Volume!$B$3:$B$68=$E28),0),MATCH($D28,Volume!$D$2:$F$2,0))</f>
         <v>5.5</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="1" t="n">
+      <c r="E29" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="H29" s="6" t="n">
-        <f aca="false" t="array" ref="H29:H29">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B29)*(Volume!$B$3:$B$68=E29),0), MATCH(D29,Volume!$D$2:$F$2,0))</f>
+      <c r="H29" s="7" t="n">
+        <f aca="false" t="array" ref="H29:H29">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B29)*(Volume!$B$3:$B$68=$E29),0),MATCH($D29,Volume!$D$2:$F$2,0))</f>
         <v>2.75</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="1" t="n">
+      <c r="E30" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H30" s="6" t="n">
-        <f aca="false" t="array" ref="H30:H30">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B30)*(Volume!$B$3:$B$68=E30),0), MATCH(D30,Volume!$D$2:$F$2,0))</f>
+      <c r="H30" s="7" t="n">
+        <f aca="false" t="array" ref="H30:H30">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B30)*(Volume!$B$3:$B$68=$E30),0),MATCH($D30,Volume!$D$2:$F$2,0))</f>
         <v>3.75</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="1" t="n">
+      <c r="E31" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H31" s="6" t="n">
-        <f aca="false" t="array" ref="H31:H31">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B31)*(Volume!$B$3:$B$68=E31),0), MATCH(D31,Volume!$D$2:$F$2,0))</f>
+      <c r="H31" s="7" t="n">
+        <f aca="false" t="array" ref="H31:H31">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B31)*(Volume!$B$3:$B$68=$E31),0),MATCH($D31,Volume!$D$2:$F$2,0))</f>
         <v>1.5</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="1" t="n">
+      <c r="E32" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H32" s="6" t="n">
-        <f aca="false" t="array" ref="H32:H32">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B32)*(Volume!$B$3:$B$68=E32),0), MATCH(D32,Volume!$D$2:$F$2,0))</f>
+      <c r="H32" s="7" t="n">
+        <f aca="false" t="array" ref="H32:H32">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B32)*(Volume!$B$3:$B$68=$E32),0),MATCH($D32,Volume!$D$2:$F$2,0))</f>
         <v>3</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="1" t="n">
+      <c r="E33" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H33" s="6" t="n">
-        <f aca="false" t="array" ref="H33:H33">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B33)*(Volume!$B$3:$B$68=E33),0), MATCH(D33,Volume!$D$2:$F$2,0))</f>
+      <c r="H33" s="7" t="n">
+        <f aca="false" t="array" ref="H33:H33">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B33)*(Volume!$B$3:$B$68=$E33),0),MATCH($D33,Volume!$D$2:$F$2,0))</f>
         <v>2</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="1" t="n">
+      <c r="E34" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="2" t="n">
         <v>975</v>
       </c>
-      <c r="H34" s="6" t="n">
-        <f aca="false" t="array" ref="H34:H34">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B34)*(Volume!$B$3:$B$68=E34),0), MATCH(D34,Volume!$D$2:$F$2,0))</f>
+      <c r="H34" s="7" t="n">
+        <f aca="false" t="array" ref="H34:H34">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B34)*(Volume!$B$3:$B$68=$E34),0),MATCH($D34,Volume!$D$2:$F$2,0))</f>
         <v>2.5</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="1" t="n">
+      <c r="E35" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="H35" s="6" t="n">
-        <f aca="false" t="array" ref="H35:H35">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B35)*(Volume!$B$3:$B$68=E35),0), MATCH(D35,Volume!$D$2:$F$2,0))</f>
+      <c r="H35" s="7" t="n">
+        <f aca="false" t="array" ref="H35:H35">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B35)*(Volume!$B$3:$B$68=$E35),0),MATCH($D35,Volume!$D$2:$F$2,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E36" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="1" t="n">
+      <c r="E36" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="H36" s="6" t="n">
-        <f aca="false" t="array" ref="H36:H36">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B36)*(Volume!$B$3:$B$68=E36),0), MATCH(D36,Volume!$D$2:$F$2,0))</f>
+      <c r="H36" s="7" t="n">
+        <f aca="false" t="array" ref="H36:H36">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B36)*(Volume!$B$3:$B$68=$E36),0),MATCH($D36,Volume!$D$2:$F$2,0))</f>
         <v>1.75</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="1" t="n">
+      <c r="E37" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H37" s="6" t="n">
-        <f aca="false" t="array" ref="H37:H37">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B37)*(Volume!$B$3:$B$68=E37),0), MATCH(D37,Volume!$D$2:$F$2,0))</f>
+      <c r="H37" s="7" t="n">
+        <f aca="false" t="array" ref="H37:H37">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B37)*(Volume!$B$3:$B$68=$E37),0),MATCH($D37,Volume!$D$2:$F$2,0))</f>
         <v>0.75</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="1" t="n">
+      <c r="E38" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H38" s="6" t="n">
-        <f aca="false" t="array" ref="H38:H38">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B38)*(Volume!$B$3:$B$68=E38),0), MATCH(D38,Volume!$D$2:$F$2,0))</f>
+      <c r="H38" s="7" t="n">
+        <f aca="false" t="array" ref="H38:H38">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B38)*(Volume!$B$3:$B$68=$E38),0),MATCH($D38,Volume!$D$2:$F$2,0))</f>
         <v>0.75</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="1" t="n">
+      <c r="E39" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="H39" s="6" t="n">
-        <f aca="false" t="array" ref="H39:H39">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B39)*(Volume!$B$3:$B$68=E39),0), MATCH(D39,Volume!$D$2:$F$2,0))</f>
+      <c r="H39" s="7" t="n">
+        <f aca="false" t="array" ref="H39:H39">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B39)*(Volume!$B$3:$B$68=$E39),0),MATCH($D39,Volume!$D$2:$F$2,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="1" t="n">
+      <c r="E40" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H40" s="6" t="n">
-        <f aca="false" t="array" ref="H40:H40">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B40)*(Volume!$B$3:$B$68=E40),0), MATCH(D40,Volume!$D$2:$F$2,0))</f>
+      <c r="H40" s="7" t="n">
+        <f aca="false" t="array" ref="H40:H40">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B40)*(Volume!$B$3:$B$68=$E40),0),MATCH($D40,Volume!$D$2:$F$2,0))</f>
         <v>0.75</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" s="1" t="n">
+      <c r="E41" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H41" s="6" t="n">
-        <f aca="false" t="array" ref="H41:H41">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B41)*(Volume!$B$3:$B$68=E41),0), MATCH(D41,Volume!$D$2:$F$2,0))</f>
+      <c r="H41" s="7" t="n">
+        <f aca="false" t="array" ref="H41:H41">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B41)*(Volume!$B$3:$B$68=$E41),0),MATCH($D41,Volume!$D$2:$F$2,0))</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="1" t="n">
+      <c r="E42" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H42" s="6" t="n">
-        <f aca="false" t="array" ref="H42:H42">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B42)*(Volume!$B$3:$B$68=E42),0), MATCH(D42,Volume!$D$2:$F$2,0))</f>
+      <c r="H42" s="7" t="n">
+        <f aca="false" t="array" ref="H42:H42">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B42)*(Volume!$B$3:$B$68=$E42),0),MATCH($D42,Volume!$D$2:$F$2,0))</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" s="1" t="n">
+      <c r="E43" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H43" s="6" t="n">
-        <f aca="false" t="array" ref="H43:H43">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B43)*(Volume!$B$3:$B$68=E43),0), MATCH(D43,Volume!$D$2:$F$2,0))</f>
+      <c r="H43" s="7" t="n">
+        <f aca="false" t="array" ref="H43:H43">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B43)*(Volume!$B$3:$B$68=$E43),0),MATCH($D43,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="1" t="n">
+      <c r="E44" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H44" s="6" t="n">
-        <f aca="false" t="array" ref="H44:H44">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B44)*(Volume!$B$3:$B$68=E44),0), MATCH(D44,Volume!$D$2:$F$2,0))</f>
+      <c r="H44" s="7" t="n">
+        <f aca="false" t="array" ref="H44:H44">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B44)*(Volume!$B$3:$B$68=$E44),0),MATCH($D44,Volume!$D$2:$F$2,0))</f>
         <v>43.25</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D45" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="1" t="n">
+      <c r="E45" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H45" s="6" t="n">
-        <f aca="false" t="array" ref="H45:H45">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B45)*(Volume!$B$3:$B$68=E45),0), MATCH(D45,Volume!$D$2:$F$2,0))</f>
+      <c r="H45" s="7" t="n">
+        <f aca="false" t="array" ref="H45:H45">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B45)*(Volume!$B$3:$B$68=$E45),0),MATCH($D45,Volume!$D$2:$F$2,0))</f>
         <v>36.25</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D46" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E46" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="1" t="n">
+      <c r="E46" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H46" s="6" t="n">
-        <f aca="false" t="array" ref="H46:H46">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B46)*(Volume!$B$3:$B$68=E46),0), MATCH(D46,Volume!$D$2:$F$2,0))</f>
+      <c r="H46" s="7" t="n">
+        <f aca="false" t="array" ref="H46:H46">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B46)*(Volume!$B$3:$B$68=$E46),0),MATCH($D46,Volume!$D$2:$F$2,0))</f>
         <v>7.25</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E47" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="1" t="n">
+      <c r="E47" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H47" s="6" t="n">
-        <f aca="false" t="array" ref="H47:H47">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B47)*(Volume!$B$3:$B$68=E47),0), MATCH(D47,Volume!$D$2:$F$2,0))</f>
+      <c r="H47" s="7" t="n">
+        <f aca="false" t="array" ref="H47:H47">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B47)*(Volume!$B$3:$B$68=$E47),0),MATCH($D47,Volume!$D$2:$F$2,0))</f>
         <v>11.25</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D48" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="1" t="n">
+      <c r="E48" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H48" s="6" t="n">
-        <f aca="false" t="array" ref="H48:H48">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B48)*(Volume!$B$3:$B$68=E48),0), MATCH(D48,Volume!$D$2:$F$2,0))</f>
+      <c r="H48" s="7" t="n">
+        <f aca="false" t="array" ref="H48:H48">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B48)*(Volume!$B$3:$B$68=$E48),0),MATCH($D48,Volume!$D$2:$F$2,0))</f>
         <v>4.5</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D49" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="1" t="n">
+      <c r="E49" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H49" s="6" t="n">
-        <f aca="false" t="array" ref="H49:H49">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B49)*(Volume!$B$3:$B$68=E49),0), MATCH(D49,Volume!$D$2:$F$2,0))</f>
+      <c r="H49" s="7" t="n">
+        <f aca="false" t="array" ref="H49:H49">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B49)*(Volume!$B$3:$B$68=$E49),0),MATCH($D49,Volume!$D$2:$F$2,0))</f>
         <v>1.75</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="1" t="n">
+      <c r="E50" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="H50" s="6" t="n">
-        <f aca="false" t="array" ref="H50:H50">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B50)*(Volume!$B$3:$B$68=E50),0), MATCH(D50,Volume!$D$2:$F$2,0))</f>
+      <c r="H50" s="7" t="n">
+        <f aca="false" t="array" ref="H50:H50">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B50)*(Volume!$B$3:$B$68=$E50),0),MATCH($D50,Volume!$D$2:$F$2,0))</f>
         <v>2.5</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="D51" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="1" t="n">
+      <c r="E51" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H51" s="6" t="n">
-        <f aca="false" t="array" ref="H51:H51">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B51)*(Volume!$B$3:$B$68=E51),0), MATCH(D51,Volume!$D$2:$F$2,0))</f>
+      <c r="H51" s="7" t="n">
+        <f aca="false" t="array" ref="H51:H51">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B51)*(Volume!$B$3:$B$68=$E51),0),MATCH($D51,Volume!$D$2:$F$2,0))</f>
         <v>1.75</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="D52" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E52" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="1" t="n">
+      <c r="E52" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H52" s="6" t="n">
-        <f aca="false" t="array" ref="H52:H52">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B52)*(Volume!$B$3:$B$68=E52),0), MATCH(D52,Volume!$D$2:$F$2,0))</f>
+      <c r="H52" s="7" t="n">
+        <f aca="false" t="array" ref="H52:H52">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B52)*(Volume!$B$3:$B$68=$E52),0),MATCH($D52,Volume!$D$2:$F$2,0))</f>
         <v>1.25</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D53" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E53" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" s="1" t="n">
+      <c r="E53" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H53" s="6" t="n">
-        <f aca="false" t="array" ref="H53:H53">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B53)*(Volume!$B$3:$B$68=E53),0), MATCH(D53,Volume!$D$2:$F$2,0))</f>
+      <c r="H53" s="7" t="n">
+        <f aca="false" t="array" ref="H53:H53">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B53)*(Volume!$B$3:$B$68=$E53),0),MATCH($D53,Volume!$D$2:$F$2,0))</f>
         <v>1.5</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="D54" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E54" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="1" t="n">
+      <c r="E54" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H54" s="6" t="n">
-        <f aca="false" t="array" ref="H54:H54">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B54)*(Volume!$B$3:$B$68=E54),0), MATCH(D54,Volume!$D$2:$F$2,0))</f>
+      <c r="H54" s="7" t="n">
+        <f aca="false" t="array" ref="H54:H54">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B54)*(Volume!$B$3:$B$68=$E54),0),MATCH($D54,Volume!$D$2:$F$2,0))</f>
         <v>2.25</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="D55" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E55" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G55" s="1" t="n">
+      <c r="E55" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="2" t="n">
         <v>975</v>
       </c>
-      <c r="H55" s="6" t="n">
-        <f aca="false" t="array" ref="H55:H55">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B55)*(Volume!$B$3:$B$68=E55),0), MATCH(D55,Volume!$D$2:$F$2,0))</f>
+      <c r="H55" s="7" t="n">
+        <f aca="false" t="array" ref="H55:H55">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B55)*(Volume!$B$3:$B$68=$E55),0),MATCH($D55,Volume!$D$2:$F$2,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D56" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E56" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="1" t="n">
+      <c r="E56" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="H56" s="6" t="n">
-        <f aca="false" t="array" ref="H56:H56">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B56)*(Volume!$B$3:$B$68=E56),0), MATCH(D56,Volume!$D$2:$F$2,0))</f>
+      <c r="H56" s="7" t="n">
+        <f aca="false" t="array" ref="H56:H56">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B56)*(Volume!$B$3:$B$68=$E56),0),MATCH($D56,Volume!$D$2:$F$2,0))</f>
         <v>1.5</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D57" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G57" s="1" t="n">
+      <c r="E57" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="H57" s="6" t="n">
-        <f aca="false" t="array" ref="H57:H57">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B57)*(Volume!$B$3:$B$68=E57),0), MATCH(D57,Volume!$D$2:$F$2,0))</f>
+      <c r="H57" s="7" t="n">
+        <f aca="false" t="array" ref="H57:H57">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B57)*(Volume!$B$3:$B$68=$E57),0),MATCH($D57,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D58" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" s="1" t="n">
+      <c r="E58" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H58" s="6" t="n">
-        <f aca="false" t="array" ref="H58:H58">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B58)*(Volume!$B$3:$B$68=E58),0), MATCH(D58,Volume!$D$2:$F$2,0))</f>
+      <c r="H58" s="7" t="n">
+        <f aca="false" t="array" ref="H58:H58">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B58)*(Volume!$B$3:$B$68=$E58),0),MATCH($D58,Volume!$D$2:$F$2,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="D59" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E59" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G59" s="1" t="n">
+      <c r="E59" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H59" s="6" t="n">
-        <f aca="false" t="array" ref="H59:H59">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B59)*(Volume!$B$3:$B$68=E59),0), MATCH(D59,Volume!$D$2:$F$2,0))</f>
+      <c r="H59" s="7" t="n">
+        <f aca="false" t="array" ref="H59:H59">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B59)*(Volume!$B$3:$B$68=$E59),0),MATCH($D59,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="D60" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E60" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" s="1" t="n">
+      <c r="E60" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="H60" s="6" t="n">
-        <f aca="false" t="array" ref="H60:H60">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B60)*(Volume!$B$3:$B$68=E60),0), MATCH(D60,Volume!$D$2:$F$2,0))</f>
+      <c r="H60" s="7" t="n">
+        <f aca="false" t="array" ref="H60:H60">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B60)*(Volume!$B$3:$B$68=$E60),0),MATCH($D60,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C61" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="D61" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E61" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G61" s="1" t="n">
+      <c r="E61" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H61" s="6" t="n">
-        <f aca="false" t="array" ref="H61:H61">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B61)*(Volume!$B$3:$B$68=E61),0), MATCH(D61,Volume!$D$2:$F$2,0))</f>
+      <c r="H61" s="7" t="n">
+        <f aca="false" t="array" ref="H61:H61">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B61)*(Volume!$B$3:$B$68=$E61),0),MATCH($D61,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="D62" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" s="1" t="n">
+      <c r="E62" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H62" s="6" t="n">
-        <f aca="false" t="array" ref="H62:H62">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B62)*(Volume!$B$3:$B$68=E62),0), MATCH(D62,Volume!$D$2:$F$2,0))</f>
+      <c r="H62" s="7" t="n">
+        <f aca="false" t="array" ref="H62:H62">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B62)*(Volume!$B$3:$B$68=$E62),0),MATCH($D62,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C63" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D63" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G63" s="1" t="n">
+      <c r="E63" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H63" s="6" t="n">
-        <f aca="false" t="array" ref="H63:H63">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B63)*(Volume!$B$3:$B$68=E63),0), MATCH(D63,Volume!$D$2:$F$2,0))</f>
+      <c r="H63" s="7" t="n">
+        <f aca="false" t="array" ref="H63:H63">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B63)*(Volume!$B$3:$B$68=$E63),0),MATCH($D63,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B64" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E64" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" s="1" t="n">
+      <c r="E64" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H64" s="6" t="n">
-        <f aca="false" t="array" ref="H64:H64">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B64)*(Volume!$B$3:$B$68=E64),0), MATCH(D64,Volume!$D$2:$F$2,0))</f>
+      <c r="H64" s="7" t="n">
+        <f aca="false" t="array" ref="H64:H64">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B64)*(Volume!$B$3:$B$68=$E64),0),MATCH($D64,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B65" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C65" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="D65" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E65" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G65" s="1" t="n">
+      <c r="E65" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H65" s="6" t="n">
-        <f aca="false" t="array" ref="H65:H65">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B65)*(Volume!$B$3:$B$68=E65),0), MATCH(D65,Volume!$D$2:$F$2,0))</f>
+      <c r="H65" s="7" t="n">
+        <f aca="false" t="array" ref="H65:H65">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B65)*(Volume!$B$3:$B$68=$E65),0),MATCH($D65,Volume!$D$2:$F$2,0))</f>
         <v>42.25</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C66" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="D66" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E66" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="1" t="n">
+      <c r="E66" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H66" s="6" t="n">
-        <f aca="false" t="array" ref="H66:H66">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B66)*(Volume!$B$3:$B$68=E66),0), MATCH(D66,Volume!$D$2:$F$2,0))</f>
+      <c r="H66" s="7" t="n">
+        <f aca="false" t="array" ref="H66:H66">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B66)*(Volume!$B$3:$B$68=$E66),0),MATCH($D66,Volume!$D$2:$F$2,0))</f>
         <v>28</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5" t="s">
+      <c r="A67" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C67" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="D67" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G67" s="1" t="n">
+      <c r="E67" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="H67" s="6" t="n">
-        <f aca="false" t="array" ref="H67:H67">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B67)*(Volume!$B$3:$B$68=E67),0), MATCH(D67,Volume!$D$2:$F$2,0))</f>
+      <c r="H67" s="7" t="n">
+        <f aca="false" t="array" ref="H67:H67">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B67)*(Volume!$B$3:$B$68=$E67),0),MATCH($D67,Volume!$D$2:$F$2,0))</f>
         <v>8.5</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="C68" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D68" s="5" t="s">
+      <c r="D68" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E68" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G68" s="1" t="n">
+      <c r="E68" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="H68" s="6" t="n">
-        <f aca="false" t="array" ref="H68:H68">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B68)*(Volume!$B$3:$B$68=E68),0), MATCH(D68,Volume!$D$2:$F$2,0))</f>
+      <c r="H68" s="7" t="n">
+        <f aca="false" t="array" ref="H68:H68">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B68)*(Volume!$B$3:$B$68=$E68),0),MATCH($D68,Volume!$D$2:$F$2,0))</f>
         <v>8.5</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5" t="s">
+      <c r="A69" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="C69" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="D69" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E69" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G69" s="1" t="n">
+      <c r="E69" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H69" s="6" t="n">
-        <f aca="false" t="array" ref="H69:H69">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B69)*(Volume!$B$3:$B$68=E69),0), MATCH(D69,Volume!$D$2:$F$2,0))</f>
+      <c r="H69" s="7" t="n">
+        <f aca="false" t="array" ref="H69:H69">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B69)*(Volume!$B$3:$B$68=$E69),0),MATCH($D69,Volume!$D$2:$F$2,0))</f>
         <v>8.75</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="C70" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D70" s="5" t="s">
+      <c r="D70" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E70" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" s="1" t="n">
+      <c r="E70" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H70" s="6" t="n">
-        <f aca="false" t="array" ref="H70:H70">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B70)*(Volume!$B$3:$B$68=E70),0), MATCH(D70,Volume!$D$2:$F$2,0))</f>
+      <c r="H70" s="7" t="n">
+        <f aca="false" t="array" ref="H70:H70">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B70)*(Volume!$B$3:$B$68=$E70),0),MATCH($D70,Volume!$D$2:$F$2,0))</f>
         <v>2.75</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5" t="s">
+      <c r="A71" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B71" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C71" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D71" s="5" t="s">
+      <c r="D71" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E71" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G71" s="1" t="n">
+      <c r="E71" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H71" s="6" t="n">
-        <f aca="false" t="array" ref="H71:H71">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B71)*(Volume!$B$3:$B$68=E71),0), MATCH(D71,Volume!$D$2:$F$2,0))</f>
+      <c r="H71" s="7" t="n">
+        <f aca="false" t="array" ref="H71:H71">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B71)*(Volume!$B$3:$B$68=$E71),0),MATCH($D71,Volume!$D$2:$F$2,0))</f>
         <v>2.75</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C72" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D72" s="5" t="s">
+      <c r="D72" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E72" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G72" s="1" t="n">
+      <c r="E72" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H72" s="6" t="n">
-        <f aca="false" t="array" ref="H72:H72">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B72)*(Volume!$B$3:$B$68=E72),0), MATCH(D72,Volume!$D$2:$F$2,0))</f>
+      <c r="H72" s="7" t="n">
+        <f aca="false" t="array" ref="H72:H72">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B72)*(Volume!$B$3:$B$68=$E72),0),MATCH($D72,Volume!$D$2:$F$2,0))</f>
         <v>3</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="5" t="s">
+      <c r="A73" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B73" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C73" s="5" t="s">
+      <c r="C73" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D73" s="5" t="s">
+      <c r="D73" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E73" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G73" s="1" t="n">
+      <c r="E73" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H73" s="6" t="n">
-        <f aca="false" t="array" ref="H73:H73">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B73)*(Volume!$B$3:$B$68=E73),0), MATCH(D73,Volume!$D$2:$F$2,0))</f>
+      <c r="H73" s="7" t="n">
+        <f aca="false" t="array" ref="H73:H73">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B73)*(Volume!$B$3:$B$68=$E73),0),MATCH($D73,Volume!$D$2:$F$2,0))</f>
         <v>2.25</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="D74" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E74" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G74" s="1" t="n">
+      <c r="E74" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H74" s="6" t="n">
-        <f aca="false" t="array" ref="H74:H74">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B74)*(Volume!$B$3:$B$68=E74),0), MATCH(D74,Volume!$D$2:$F$2,0))</f>
+      <c r="H74" s="7" t="n">
+        <f aca="false" t="array" ref="H74:H74">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B74)*(Volume!$B$3:$B$68=$E74),0),MATCH($D74,Volume!$D$2:$F$2,0))</f>
         <v>6</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="5" t="s">
+      <c r="A75" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="B75" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="C75" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="D75" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E75" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G75" s="1" t="n">
+      <c r="E75" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H75" s="6" t="n">
-        <f aca="false" t="array" ref="H75:H75">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B75)*(Volume!$B$3:$B$68=E75),0), MATCH(D75,Volume!$D$2:$F$2,0))</f>
+      <c r="H75" s="7" t="n">
+        <f aca="false" t="array" ref="H75:H75">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B75)*(Volume!$B$3:$B$68=$E75),0),MATCH($D75,Volume!$D$2:$F$2,0))</f>
         <v>1.75</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="D76" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E76" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G76" s="1" t="n">
+      <c r="E76" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H76" s="6" t="n">
-        <f aca="false" t="array" ref="H76:H76">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B76)*(Volume!$B$3:$B$68=E76),0), MATCH(D76,Volume!$D$2:$F$2,0))</f>
+      <c r="H76" s="7" t="n">
+        <f aca="false" t="array" ref="H76:H76">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B76)*(Volume!$B$3:$B$68=$E76),0),MATCH($D76,Volume!$D$2:$F$2,0))</f>
         <v>2</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="5" t="s">
+      <c r="A77" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B77" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="C77" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="D77" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E77" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G77" s="1" t="n">
+      <c r="E77" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="2" t="n">
         <v>575</v>
       </c>
-      <c r="H77" s="6" t="n">
-        <f aca="false" t="array" ref="H77:H77">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B77)*(Volume!$B$3:$B$68=E77),0), MATCH(D77,Volume!$D$2:$F$2,0))</f>
+      <c r="H77" s="7" t="n">
+        <f aca="false" t="array" ref="H77:H77">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B77)*(Volume!$B$3:$B$68=$E77),0),MATCH($D77,Volume!$D$2:$F$2,0))</f>
         <v>1.75</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="5" t="s">
+      <c r="A78" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B78" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C78" s="5" t="s">
+      <c r="C78" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D78" s="5" t="s">
+      <c r="D78" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E78" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G78" s="1" t="n">
+      <c r="E78" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="H78" s="6" t="n">
-        <f aca="false" t="array" ref="H78:H78">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B78)*(Volume!$B$3:$B$68=E78),0), MATCH(D78,Volume!$D$2:$F$2,0))</f>
+      <c r="H78" s="7" t="n">
+        <f aca="false" t="array" ref="H78:H78">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B78)*(Volume!$B$3:$B$68=$E78),0),MATCH($D78,Volume!$D$2:$F$2,0))</f>
         <v>1.25</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="5" t="s">
+      <c r="A79" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="C79" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D79" s="5" t="s">
+      <c r="D79" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E79" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G79" s="1" t="n">
+      <c r="E79" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H79" s="6" t="n">
-        <f aca="false" t="array" ref="H79:H79">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B79)*(Volume!$B$3:$B$68=E79),0), MATCH(D79,Volume!$D$2:$F$2,0))</f>
+      <c r="H79" s="7" t="n">
+        <f aca="false" t="array" ref="H79:H79">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B79)*(Volume!$B$3:$B$68=$E79),0),MATCH($D79,Volume!$D$2:$F$2,0))</f>
         <v>1.25</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="5" t="s">
+      <c r="A80" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="B80" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="C80" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D80" s="5" t="s">
+      <c r="D80" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E80" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G80" s="1" t="n">
+      <c r="E80" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H80" s="6" t="n">
-        <f aca="false" t="array" ref="H80:H80">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B80)*(Volume!$B$3:$B$68=E80),0), MATCH(D80,Volume!$D$2:$F$2,0))</f>
+      <c r="H80" s="7" t="n">
+        <f aca="false" t="array" ref="H80:H80">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B80)*(Volume!$B$3:$B$68=$E80),0),MATCH($D80,Volume!$D$2:$F$2,0))</f>
         <v>1.5</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="5" t="s">
+      <c r="A81" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="B81" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="C81" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D81" s="5" t="s">
+      <c r="D81" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E81" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G81" s="1" t="n">
+      <c r="E81" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="H81" s="6" t="n">
-        <f aca="false" t="array" ref="H81:H81">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B81)*(Volume!$B$3:$B$68=E81),0), MATCH(D81,Volume!$D$2:$F$2,0))</f>
+      <c r="H81" s="7" t="n">
+        <f aca="false" t="array" ref="H81:H81">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B81)*(Volume!$B$3:$B$68=$E81),0),MATCH($D81,Volume!$D$2:$F$2,0))</f>
         <v>1.25</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="5" t="s">
+      <c r="A82" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C82" s="5" t="s">
+      <c r="C82" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="D82" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E82" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G82" s="1" t="n">
+      <c r="E82" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H82" s="6" t="n">
-        <f aca="false" t="array" ref="H82:H82">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B82)*(Volume!$B$3:$B$68=E82),0), MATCH(D82,Volume!$D$2:$F$2,0))</f>
+      <c r="H82" s="7" t="n">
+        <f aca="false" t="array" ref="H82:H82">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B82)*(Volume!$B$3:$B$68=$E82),0),MATCH($D82,Volume!$D$2:$F$2,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="5" t="s">
+      <c r="A83" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="B83" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C83" s="5" t="s">
+      <c r="C83" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D83" s="5" t="s">
+      <c r="D83" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E83" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G83" s="1" t="n">
+      <c r="E83" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H83" s="6" t="n">
-        <f aca="false" t="array" ref="H83:H83">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B83)*(Volume!$B$3:$B$68=E83),0), MATCH(D83,Volume!$D$2:$F$2,0))</f>
+      <c r="H83" s="7" t="n">
+        <f aca="false" t="array" ref="H83:H83">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B83)*(Volume!$B$3:$B$68=$E83),0),MATCH($D83,Volume!$D$2:$F$2,0))</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="5" t="s">
+      <c r="A84" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="B84" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C84" s="5" t="s">
+      <c r="C84" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="5" t="s">
+      <c r="D84" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E84" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G84" s="1" t="n">
+      <c r="E84" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H84" s="6" t="n">
-        <f aca="false" t="array" ref="H84:H84">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B84)*(Volume!$B$3:$B$68=E84),0), MATCH(D84,Volume!$D$2:$F$2,0))</f>
+      <c r="H84" s="7" t="n">
+        <f aca="false" t="array" ref="H84:H84">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B84)*(Volume!$B$3:$B$68=$E84),0),MATCH($D84,Volume!$D$2:$F$2,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="5" t="s">
+      <c r="A85" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B85" s="5" t="s">
+      <c r="B85" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C85" s="5" t="s">
+      <c r="C85" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D85" s="5" t="s">
+      <c r="D85" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E85" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G85" s="1" t="n">
+      <c r="E85" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H85" s="6" t="n">
-        <f aca="false" t="array" ref="H85:H85">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B85)*(Volume!$B$3:$B$68=E85),0), MATCH(D85,Volume!$D$2:$F$2,0))</f>
+      <c r="H85" s="7" t="n">
+        <f aca="false" t="array" ref="H85:H85">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B85)*(Volume!$B$3:$B$68=$E85),0),MATCH($D85,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="5" t="s">
+      <c r="A86" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="B86" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C86" s="5" t="s">
+      <c r="C86" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D86" s="5" t="s">
+      <c r="D86" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E86" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G86" s="1" t="n">
+      <c r="E86" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H86" s="6" t="n">
-        <f aca="false" t="array" ref="H86:H86">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B86)*(Volume!$B$3:$B$68=E86),0), MATCH(D86,Volume!$D$2:$F$2,0))</f>
+      <c r="H86" s="7" t="n">
+        <f aca="false" t="array" ref="H86:H86">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B86)*(Volume!$B$3:$B$68=$E86),0),MATCH($D86,Volume!$D$2:$F$2,0))</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="5" t="s">
+      <c r="A87" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="B87" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C87" s="5" t="s">
+      <c r="C87" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D87" s="5" t="s">
+      <c r="D87" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E87" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G87" s="1" t="n">
+      <c r="E87" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H87" s="6" t="n">
-        <f aca="false" t="array" ref="H87:H87">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B87)*(Volume!$B$3:$B$68=E87),0), MATCH(D87,Volume!$D$2:$F$2,0))</f>
+      <c r="H87" s="7" t="n">
+        <f aca="false" t="array" ref="H87:H87">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B87)*(Volume!$B$3:$B$68=$E87),0),MATCH($D87,Volume!$D$2:$F$2,0))</f>
         <v>60</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="5" t="s">
+      <c r="A88" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C88" s="5" t="s">
+      <c r="C88" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D88" s="5" t="s">
+      <c r="D88" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E88" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G88" s="1" t="n">
+      <c r="E88" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H88" s="6" t="n">
-        <f aca="false" t="array" ref="H88:H88">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B88)*(Volume!$B$3:$B$68=E88),0), MATCH(D88,Volume!$D$2:$F$2,0))</f>
+      <c r="H88" s="7" t="n">
+        <f aca="false" t="array" ref="H88:H88">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B88)*(Volume!$B$3:$B$68=$E88),0),MATCH($D88,Volume!$D$2:$F$2,0))</f>
         <v>33</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="5" t="s">
+      <c r="A89" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="B89" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="C89" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D89" s="5" t="s">
+      <c r="D89" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E89" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G89" s="1" t="n">
+      <c r="E89" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H89" s="6" t="n">
-        <f aca="false" t="array" ref="H89:H89">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B89)*(Volume!$B$3:$B$68=E89),0), MATCH(D89,Volume!$D$2:$F$2,0))</f>
+      <c r="H89" s="7" t="n">
+        <f aca="false" t="array" ref="H89:H89">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B89)*(Volume!$B$3:$B$68=$E89),0),MATCH($D89,Volume!$D$2:$F$2,0))</f>
         <v>9</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="5" t="s">
+      <c r="A90" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="C90" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D90" s="5" t="s">
+      <c r="D90" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E90" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G90" s="1" t="n">
+      <c r="E90" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H90" s="6" t="n">
-        <f aca="false" t="array" ref="H90:H90">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B90)*(Volume!$B$3:$B$68=E90),0), MATCH(D90,Volume!$D$2:$F$2,0))</f>
+      <c r="H90" s="7" t="n">
+        <f aca="false" t="array" ref="H90:H90">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B90)*(Volume!$B$3:$B$68=$E90),0),MATCH($D90,Volume!$D$2:$F$2,0))</f>
         <v>2.25</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="5" t="s">
+      <c r="A91" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="B91" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="C91" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D91" s="5" t="s">
+      <c r="D91" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E91" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G91" s="1" t="n">
+      <c r="E91" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G91" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H91" s="6" t="n">
-        <f aca="false" t="array" ref="H91:H91">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B91)*(Volume!$B$3:$B$68=E91),0), MATCH(D91,Volume!$D$2:$F$2,0))</f>
+      <c r="H91" s="7" t="n">
+        <f aca="false" t="array" ref="H91:H91">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B91)*(Volume!$B$3:$B$68=$E91),0),MATCH($D91,Volume!$D$2:$F$2,0))</f>
         <v>8.5</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="5" t="s">
+      <c r="A92" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="B92" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="C92" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D92" s="5" t="s">
+      <c r="D92" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E92" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G92" s="1" t="n">
+      <c r="E92" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H92" s="6" t="n">
-        <f aca="false" t="array" ref="H92:H92">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B92)*(Volume!$B$3:$B$68=E92),0), MATCH(D92,Volume!$D$2:$F$2,0))</f>
+      <c r="H92" s="7" t="n">
+        <f aca="false" t="array" ref="H92:H92">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B92)*(Volume!$B$3:$B$68=$E92),0),MATCH($D92,Volume!$D$2:$F$2,0))</f>
         <v>5.5</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="5" t="s">
+      <c r="A93" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B93" s="5" t="s">
+      <c r="B93" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C93" s="5" t="s">
+      <c r="C93" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D93" s="5" t="s">
+      <c r="D93" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E93" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G93" s="1" t="n">
+      <c r="E93" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="H93" s="6" t="n">
-        <f aca="false" t="array" ref="H93:H93">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B93)*(Volume!$B$3:$B$68=E93),0), MATCH(D93,Volume!$D$2:$F$2,0))</f>
+      <c r="H93" s="7" t="n">
+        <f aca="false" t="array" ref="H93:H93">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B93)*(Volume!$B$3:$B$68=$E93),0),MATCH($D93,Volume!$D$2:$F$2,0))</f>
         <v>2.75</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="5" t="s">
+      <c r="A94" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B94" s="5" t="s">
+      <c r="B94" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C94" s="5" t="s">
+      <c r="C94" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D94" s="5" t="s">
+      <c r="D94" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E94" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G94" s="1" t="n">
+      <c r="E94" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H94" s="6" t="n">
-        <f aca="false" t="array" ref="H94:H94">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B94)*(Volume!$B$3:$B$68=E94),0), MATCH(D94,Volume!$D$2:$F$2,0))</f>
+      <c r="H94" s="7" t="n">
+        <f aca="false" t="array" ref="H94:H94">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B94)*(Volume!$B$3:$B$68=$E94),0),MATCH($D94,Volume!$D$2:$F$2,0))</f>
         <v>3.75</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="5" t="s">
+      <c r="A95" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B95" s="5" t="s">
+      <c r="B95" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C95" s="5" t="s">
+      <c r="C95" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D95" s="5" t="s">
+      <c r="D95" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E95" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G95" s="1" t="n">
+      <c r="E95" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G95" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H95" s="6" t="n">
-        <f aca="false" t="array" ref="H95:H95">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B95)*(Volume!$B$3:$B$68=E95),0), MATCH(D95,Volume!$D$2:$F$2,0))</f>
+      <c r="H95" s="7" t="n">
+        <f aca="false" t="array" ref="H95:H95">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B95)*(Volume!$B$3:$B$68=$E95),0),MATCH($D95,Volume!$D$2:$F$2,0))</f>
         <v>1.5</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="5" t="s">
+      <c r="A96" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B96" s="5" t="s">
+      <c r="B96" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C96" s="5" t="s">
+      <c r="C96" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D96" s="5" t="s">
+      <c r="D96" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E96" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G96" s="1" t="n">
+      <c r="E96" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G96" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H96" s="6" t="n">
-        <f aca="false" t="array" ref="H96:H96">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B96)*(Volume!$B$3:$B$68=E96),0), MATCH(D96,Volume!$D$2:$F$2,0))</f>
+      <c r="H96" s="7" t="n">
+        <f aca="false" t="array" ref="H96:H96">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B96)*(Volume!$B$3:$B$68=$E96),0),MATCH($D96,Volume!$D$2:$F$2,0))</f>
         <v>3</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="5" t="s">
+      <c r="A97" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B97" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C97" s="5" t="s">
+      <c r="C97" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D97" s="5" t="s">
+      <c r="D97" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E97" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G97" s="1" t="n">
+      <c r="E97" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G97" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H97" s="6" t="n">
-        <f aca="false" t="array" ref="H97:H97">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B97)*(Volume!$B$3:$B$68=E97),0), MATCH(D97,Volume!$D$2:$F$2,0))</f>
+      <c r="H97" s="7" t="n">
+        <f aca="false" t="array" ref="H97:H97">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B97)*(Volume!$B$3:$B$68=$E97),0),MATCH($D97,Volume!$D$2:$F$2,0))</f>
         <v>2</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="5" t="s">
+      <c r="A98" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B98" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C98" s="5" t="s">
+      <c r="C98" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D98" s="5" t="s">
+      <c r="D98" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E98" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G98" s="1" t="n">
+      <c r="E98" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" s="2" t="n">
         <v>975</v>
       </c>
-      <c r="H98" s="6" t="n">
-        <f aca="false" t="array" ref="H98:H98">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B98)*(Volume!$B$3:$B$68=E98),0), MATCH(D98,Volume!$D$2:$F$2,0))</f>
+      <c r="H98" s="7" t="n">
+        <f aca="false" t="array" ref="H98:H98">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B98)*(Volume!$B$3:$B$68=$E98),0),MATCH($D98,Volume!$D$2:$F$2,0))</f>
         <v>2.5</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="5" t="s">
+      <c r="A99" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C99" s="5" t="s">
+      <c r="C99" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D99" s="5" t="s">
+      <c r="D99" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E99" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G99" s="1" t="n">
+      <c r="E99" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G99" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="H99" s="6" t="n">
-        <f aca="false" t="array" ref="H99:H99">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B99)*(Volume!$B$3:$B$68=E99),0), MATCH(D99,Volume!$D$2:$F$2,0))</f>
+      <c r="H99" s="7" t="n">
+        <f aca="false" t="array" ref="H99:H99">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B99)*(Volume!$B$3:$B$68=$E99),0),MATCH($D99,Volume!$D$2:$F$2,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="5" t="s">
+      <c r="A100" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B100" s="5" t="s">
+      <c r="B100" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C100" s="5" t="s">
+      <c r="C100" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D100" s="5" t="s">
+      <c r="D100" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E100" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G100" s="1" t="n">
+      <c r="E100" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="H100" s="6" t="n">
-        <f aca="false" t="array" ref="H100:H100">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B100)*(Volume!$B$3:$B$68=E100),0), MATCH(D100,Volume!$D$2:$F$2,0))</f>
+      <c r="H100" s="7" t="n">
+        <f aca="false" t="array" ref="H100:H100">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B100)*(Volume!$B$3:$B$68=$E100),0),MATCH($D100,Volume!$D$2:$F$2,0))</f>
         <v>1.75</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="5" t="s">
+      <c r="A101" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B101" s="5" t="s">
+      <c r="B101" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C101" s="5" t="s">
+      <c r="C101" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D101" s="5" t="s">
+      <c r="D101" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E101" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G101" s="1" t="n">
+      <c r="E101" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H101" s="6" t="n">
-        <f aca="false" t="array" ref="H101:H101">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B101)*(Volume!$B$3:$B$68=E101),0), MATCH(D101,Volume!$D$2:$F$2,0))</f>
+      <c r="H101" s="7" t="n">
+        <f aca="false" t="array" ref="H101:H101">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B101)*(Volume!$B$3:$B$68=$E101),0),MATCH($D101,Volume!$D$2:$F$2,0))</f>
         <v>0.75</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="5" t="s">
+      <c r="A102" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B102" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C102" s="5" t="s">
+      <c r="C102" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D102" s="5" t="s">
+      <c r="D102" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E102" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G102" s="1" t="n">
+      <c r="E102" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H102" s="6" t="n">
-        <f aca="false" t="array" ref="H102:H102">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B102)*(Volume!$B$3:$B$68=E102),0), MATCH(D102,Volume!$D$2:$F$2,0))</f>
+      <c r="H102" s="7" t="n">
+        <f aca="false" t="array" ref="H102:H102">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B102)*(Volume!$B$3:$B$68=$E102),0),MATCH($D102,Volume!$D$2:$F$2,0))</f>
         <v>0.75</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="5" t="s">
+      <c r="A103" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B103" s="5" t="s">
+      <c r="B103" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C103" s="5" t="s">
+      <c r="C103" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D103" s="5" t="s">
+      <c r="D103" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E103" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G103" s="1" t="n">
+      <c r="E103" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="H103" s="6" t="n">
-        <f aca="false" t="array" ref="H103:H103">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B103)*(Volume!$B$3:$B$68=E103),0), MATCH(D103,Volume!$D$2:$F$2,0))</f>
+      <c r="H103" s="7" t="n">
+        <f aca="false" t="array" ref="H103:H103">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B103)*(Volume!$B$3:$B$68=$E103),0),MATCH($D103,Volume!$D$2:$F$2,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="5" t="s">
+      <c r="A104" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B104" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C104" s="5" t="s">
+      <c r="C104" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D104" s="5" t="s">
+      <c r="D104" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E104" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G104" s="1" t="n">
+      <c r="E104" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H104" s="6" t="n">
-        <f aca="false" t="array" ref="H104:H104">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B104)*(Volume!$B$3:$B$68=E104),0), MATCH(D104,Volume!$D$2:$F$2,0))</f>
+      <c r="H104" s="7" t="n">
+        <f aca="false" t="array" ref="H104:H104">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B104)*(Volume!$B$3:$B$68=$E104),0),MATCH($D104,Volume!$D$2:$F$2,0))</f>
         <v>0.75</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="5" t="s">
+      <c r="A105" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B105" s="5" t="s">
+      <c r="B105" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C105" s="5" t="s">
+      <c r="C105" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D105" s="5" t="s">
+      <c r="D105" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E105" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G105" s="1" t="n">
+      <c r="E105" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H105" s="6" t="n">
-        <f aca="false" t="array" ref="H105:H105">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B105)*(Volume!$B$3:$B$68=E105),0), MATCH(D105,Volume!$D$2:$F$2,0))</f>
+      <c r="H105" s="7" t="n">
+        <f aca="false" t="array" ref="H105:H105">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B105)*(Volume!$B$3:$B$68=$E105),0),MATCH($D105,Volume!$D$2:$F$2,0))</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="5" t="s">
+      <c r="A106" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B106" s="5" t="s">
+      <c r="B106" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C106" s="5" t="s">
+      <c r="C106" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D106" s="5" t="s">
+      <c r="D106" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E106" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G106" s="1" t="n">
+      <c r="E106" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H106" s="6" t="n">
-        <f aca="false" t="array" ref="H106:H106">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B106)*(Volume!$B$3:$B$68=E106),0), MATCH(D106,Volume!$D$2:$F$2,0))</f>
+      <c r="H106" s="7" t="n">
+        <f aca="false" t="array" ref="H106:H106">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B106)*(Volume!$B$3:$B$68=$E106),0),MATCH($D106,Volume!$D$2:$F$2,0))</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="5" t="s">
+      <c r="A107" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B107" s="5" t="s">
+      <c r="B107" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C107" s="5" t="s">
+      <c r="C107" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D107" s="5" t="s">
+      <c r="D107" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E107" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G107" s="1" t="n">
+      <c r="E107" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G107" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H107" s="6" t="n">
-        <f aca="false" t="array" ref="H107:H107">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B107)*(Volume!$B$3:$B$68=E107),0), MATCH(D107,Volume!$D$2:$F$2,0))</f>
+      <c r="H107" s="7" t="n">
+        <f aca="false" t="array" ref="H107:H107">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B107)*(Volume!$B$3:$B$68=$E107),0),MATCH($D107,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="5" t="s">
+      <c r="A108" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B108" s="5" t="s">
+      <c r="B108" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C108" s="5" t="s">
+      <c r="C108" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D108" s="5" t="s">
+      <c r="D108" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E108" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G108" s="1" t="n">
+      <c r="E108" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H108" s="6" t="n">
-        <f aca="false" t="array" ref="H108:H108">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B108)*(Volume!$B$3:$B$68=E108),0), MATCH(D108,Volume!$D$2:$F$2,0))</f>
+      <c r="H108" s="7" t="n">
+        <f aca="false" t="array" ref="H108:H108">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B108)*(Volume!$B$3:$B$68=$E108),0),MATCH($D108,Volume!$D$2:$F$2,0))</f>
         <v>43.25</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="5" t="s">
+      <c r="A109" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B109" s="5" t="s">
+      <c r="B109" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C109" s="5" t="s">
+      <c r="C109" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D109" s="5" t="s">
+      <c r="D109" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E109" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F109" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G109" s="1" t="n">
+      <c r="E109" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G109" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H109" s="6" t="n">
-        <f aca="false" t="array" ref="H109:H109">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B109)*(Volume!$B$3:$B$68=E109),0), MATCH(D109,Volume!$D$2:$F$2,0))</f>
+      <c r="H109" s="7" t="n">
+        <f aca="false" t="array" ref="H109:H109">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B109)*(Volume!$B$3:$B$68=$E109),0),MATCH($D109,Volume!$D$2:$F$2,0))</f>
         <v>36.25</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="5" t="s">
+      <c r="A110" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B110" s="5" t="s">
+      <c r="B110" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="5" t="s">
+      <c r="C110" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D110" s="5" t="s">
+      <c r="D110" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E110" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G110" s="1" t="n">
+      <c r="E110" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G110" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H110" s="6" t="n">
-        <f aca="false" t="array" ref="H110:H110">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B110)*(Volume!$B$3:$B$68=E110),0), MATCH(D110,Volume!$D$2:$F$2,0))</f>
+      <c r="H110" s="7" t="n">
+        <f aca="false" t="array" ref="H110:H110">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B110)*(Volume!$B$3:$B$68=$E110),0),MATCH($D110,Volume!$D$2:$F$2,0))</f>
         <v>7.25</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="5" t="s">
+      <c r="A111" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B111" s="5" t="s">
+      <c r="B111" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C111" s="5" t="s">
+      <c r="C111" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D111" s="5" t="s">
+      <c r="D111" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E111" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F111" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G111" s="1" t="n">
+      <c r="E111" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G111" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H111" s="6" t="n">
-        <f aca="false" t="array" ref="H111:H111">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B111)*(Volume!$B$3:$B$68=E111),0), MATCH(D111,Volume!$D$2:$F$2,0))</f>
+      <c r="H111" s="7" t="n">
+        <f aca="false" t="array" ref="H111:H111">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B111)*(Volume!$B$3:$B$68=$E111),0),MATCH($D111,Volume!$D$2:$F$2,0))</f>
         <v>11.25</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="5" t="s">
+      <c r="A112" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B112" s="5" t="s">
+      <c r="B112" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C112" s="5" t="s">
+      <c r="C112" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D112" s="5" t="s">
+      <c r="D112" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E112" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G112" s="1" t="n">
+      <c r="E112" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G112" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H112" s="6" t="n">
-        <f aca="false" t="array" ref="H112:H112">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B112)*(Volume!$B$3:$B$68=E112),0), MATCH(D112,Volume!$D$2:$F$2,0))</f>
+      <c r="H112" s="7" t="n">
+        <f aca="false" t="array" ref="H112:H112">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B112)*(Volume!$B$3:$B$68=$E112),0),MATCH($D112,Volume!$D$2:$F$2,0))</f>
         <v>4.5</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="5" t="s">
+      <c r="A113" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B113" s="5" t="s">
+      <c r="B113" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C113" s="5" t="s">
+      <c r="C113" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D113" s="5" t="s">
+      <c r="D113" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E113" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G113" s="1" t="n">
+      <c r="E113" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G113" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H113" s="6" t="n">
-        <f aca="false" t="array" ref="H113:H113">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B113)*(Volume!$B$3:$B$68=E113),0), MATCH(D113,Volume!$D$2:$F$2,0))</f>
+      <c r="H113" s="7" t="n">
+        <f aca="false" t="array" ref="H113:H113">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B113)*(Volume!$B$3:$B$68=$E113),0),MATCH($D113,Volume!$D$2:$F$2,0))</f>
         <v>1.75</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="5" t="s">
+      <c r="A114" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B114" s="5" t="s">
+      <c r="B114" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C114" s="5" t="s">
+      <c r="C114" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D114" s="5" t="s">
+      <c r="D114" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E114" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G114" s="1" t="n">
+      <c r="E114" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="H114" s="6" t="n">
-        <f aca="false" t="array" ref="H114:H114">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B114)*(Volume!$B$3:$B$68=E114),0), MATCH(D114,Volume!$D$2:$F$2,0))</f>
+      <c r="H114" s="7" t="n">
+        <f aca="false" t="array" ref="H114:H114">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B114)*(Volume!$B$3:$B$68=$E114),0),MATCH($D114,Volume!$D$2:$F$2,0))</f>
         <v>2.5</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="5" t="s">
+      <c r="A115" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B115" s="5" t="s">
+      <c r="B115" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C115" s="5" t="s">
+      <c r="C115" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D115" s="5" t="s">
+      <c r="D115" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E115" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F115" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G115" s="1" t="n">
+      <c r="E115" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G115" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H115" s="6" t="n">
-        <f aca="false" t="array" ref="H115:H115">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B115)*(Volume!$B$3:$B$68=E115),0), MATCH(D115,Volume!$D$2:$F$2,0))</f>
+      <c r="H115" s="7" t="n">
+        <f aca="false" t="array" ref="H115:H115">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B115)*(Volume!$B$3:$B$68=$E115),0),MATCH($D115,Volume!$D$2:$F$2,0))</f>
         <v>1.75</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="5" t="s">
+      <c r="A116" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B116" s="5" t="s">
+      <c r="B116" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C116" s="5" t="s">
+      <c r="C116" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D116" s="5" t="s">
+      <c r="D116" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E116" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F116" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G116" s="1" t="n">
+      <c r="E116" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H116" s="6" t="n">
-        <f aca="false" t="array" ref="H116:H116">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B116)*(Volume!$B$3:$B$68=E116),0), MATCH(D116,Volume!$D$2:$F$2,0))</f>
+      <c r="H116" s="7" t="n">
+        <f aca="false" t="array" ref="H116:H116">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B116)*(Volume!$B$3:$B$68=$E116),0),MATCH($D116,Volume!$D$2:$F$2,0))</f>
         <v>1.25</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="5" t="s">
+      <c r="A117" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B117" s="5" t="s">
+      <c r="B117" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C117" s="5" t="s">
+      <c r="C117" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D117" s="5" t="s">
+      <c r="D117" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E117" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F117" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G117" s="1" t="n">
+      <c r="E117" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H117" s="6" t="n">
-        <f aca="false" t="array" ref="H117:H117">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B117)*(Volume!$B$3:$B$68=E117),0), MATCH(D117,Volume!$D$2:$F$2,0))</f>
+      <c r="H117" s="7" t="n">
+        <f aca="false" t="array" ref="H117:H117">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B117)*(Volume!$B$3:$B$68=$E117),0),MATCH($D117,Volume!$D$2:$F$2,0))</f>
         <v>1.5</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="5" t="s">
+      <c r="A118" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B118" s="5" t="s">
+      <c r="B118" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C118" s="5" t="s">
+      <c r="C118" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D118" s="5" t="s">
+      <c r="D118" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E118" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G118" s="1" t="n">
+      <c r="E118" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H118" s="6" t="n">
-        <f aca="false" t="array" ref="H118:H118">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B118)*(Volume!$B$3:$B$68=E118),0), MATCH(D118,Volume!$D$2:$F$2,0))</f>
+      <c r="H118" s="7" t="n">
+        <f aca="false" t="array" ref="H118:H118">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B118)*(Volume!$B$3:$B$68=$E118),0),MATCH($D118,Volume!$D$2:$F$2,0))</f>
         <v>2.25</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="5" t="s">
+      <c r="A119" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B119" s="5" t="s">
+      <c r="B119" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C119" s="5" t="s">
+      <c r="C119" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D119" s="5" t="s">
+      <c r="D119" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E119" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F119" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G119" s="1" t="n">
+      <c r="E119" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G119" s="2" t="n">
         <v>975</v>
       </c>
-      <c r="H119" s="6" t="n">
-        <f aca="false" t="array" ref="H119:H119">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B119)*(Volume!$B$3:$B$68=E119),0), MATCH(D119,Volume!$D$2:$F$2,0))</f>
+      <c r="H119" s="7" t="n">
+        <f aca="false" t="array" ref="H119:H119">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B119)*(Volume!$B$3:$B$68=$E119),0),MATCH($D119,Volume!$D$2:$F$2,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="5" t="s">
+      <c r="A120" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B120" s="5" t="s">
+      <c r="B120" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C120" s="5" t="s">
+      <c r="C120" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D120" s="5" t="s">
+      <c r="D120" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E120" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F120" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G120" s="1" t="n">
+      <c r="E120" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G120" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="H120" s="6" t="n">
-        <f aca="false" t="array" ref="H120:H120">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B120)*(Volume!$B$3:$B$68=E120),0), MATCH(D120,Volume!$D$2:$F$2,0))</f>
+      <c r="H120" s="7" t="n">
+        <f aca="false" t="array" ref="H120:H120">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B120)*(Volume!$B$3:$B$68=$E120),0),MATCH($D120,Volume!$D$2:$F$2,0))</f>
         <v>1.5</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="5" t="s">
+      <c r="A121" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B121" s="5" t="s">
+      <c r="B121" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C121" s="5" t="s">
+      <c r="C121" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D121" s="5" t="s">
+      <c r="D121" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E121" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F121" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G121" s="1" t="n">
+      <c r="E121" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G121" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="H121" s="6" t="n">
-        <f aca="false" t="array" ref="H121:H121">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B121)*(Volume!$B$3:$B$68=E121),0), MATCH(D121,Volume!$D$2:$F$2,0))</f>
+      <c r="H121" s="7" t="n">
+        <f aca="false" t="array" ref="H121:H121">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B121)*(Volume!$B$3:$B$68=$E121),0),MATCH($D121,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="5" t="s">
+      <c r="A122" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B122" s="5" t="s">
+      <c r="B122" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C122" s="5" t="s">
+      <c r="C122" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D122" s="5" t="s">
+      <c r="D122" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E122" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G122" s="1" t="n">
+      <c r="E122" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H122" s="6" t="n">
-        <f aca="false" t="array" ref="H122:H122">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B122)*(Volume!$B$3:$B$68=E122),0), MATCH(D122,Volume!$D$2:$F$2,0))</f>
+      <c r="H122" s="7" t="n">
+        <f aca="false" t="array" ref="H122:H122">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B122)*(Volume!$B$3:$B$68=$E122),0),MATCH($D122,Volume!$D$2:$F$2,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="5" t="s">
+      <c r="A123" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B123" s="5" t="s">
+      <c r="B123" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C123" s="5" t="s">
+      <c r="C123" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D123" s="5" t="s">
+      <c r="D123" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E123" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F123" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G123" s="1" t="n">
+      <c r="E123" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G123" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H123" s="6" t="n">
-        <f aca="false" t="array" ref="H123:H123">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B123)*(Volume!$B$3:$B$68=E123),0), MATCH(D123,Volume!$D$2:$F$2,0))</f>
+      <c r="H123" s="7" t="n">
+        <f aca="false" t="array" ref="H123:H123">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B123)*(Volume!$B$3:$B$68=$E123),0),MATCH($D123,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="5" t="s">
+      <c r="A124" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B124" s="5" t="s">
+      <c r="B124" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C124" s="5" t="s">
+      <c r="C124" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D124" s="5" t="s">
+      <c r="D124" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E124" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G124" s="1" t="n">
+      <c r="E124" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G124" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="H124" s="6" t="n">
-        <f aca="false" t="array" ref="H124:H124">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B124)*(Volume!$B$3:$B$68=E124),0), MATCH(D124,Volume!$D$2:$F$2,0))</f>
+      <c r="H124" s="7" t="n">
+        <f aca="false" t="array" ref="H124:H124">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B124)*(Volume!$B$3:$B$68=$E124),0),MATCH($D124,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="5" t="s">
+      <c r="A125" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B125" s="5" t="s">
+      <c r="B125" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C125" s="5" t="s">
+      <c r="C125" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D125" s="5" t="s">
+      <c r="D125" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E125" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F125" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G125" s="1" t="n">
+      <c r="E125" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G125" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H125" s="6" t="n">
-        <f aca="false" t="array" ref="H125:H125">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B125)*(Volume!$B$3:$B$68=E125),0), MATCH(D125,Volume!$D$2:$F$2,0))</f>
+      <c r="H125" s="7" t="n">
+        <f aca="false" t="array" ref="H125:H125">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B125)*(Volume!$B$3:$B$68=$E125),0),MATCH($D125,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="5" t="s">
+      <c r="A126" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B126" s="5" t="s">
+      <c r="B126" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C126" s="5" t="s">
+      <c r="C126" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D126" s="5" t="s">
+      <c r="D126" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E126" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F126" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G126" s="1" t="n">
+      <c r="E126" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G126" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H126" s="6" t="n">
-        <f aca="false" t="array" ref="H126:H126">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B126)*(Volume!$B$3:$B$68=E126),0), MATCH(D126,Volume!$D$2:$F$2,0))</f>
+      <c r="H126" s="7" t="n">
+        <f aca="false" t="array" ref="H126:H126">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B126)*(Volume!$B$3:$B$68=$E126),0),MATCH($D126,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="5" t="s">
+      <c r="A127" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B127" s="5" t="s">
+      <c r="B127" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C127" s="5" t="s">
+      <c r="C127" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D127" s="5" t="s">
+      <c r="D127" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E127" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F127" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G127" s="1" t="n">
+      <c r="E127" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G127" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H127" s="6" t="n">
-        <f aca="false" t="array" ref="H127:H127">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B127)*(Volume!$B$3:$B$68=E127),0), MATCH(D127,Volume!$D$2:$F$2,0))</f>
+      <c r="H127" s="7" t="n">
+        <f aca="false" t="array" ref="H127:H127">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B127)*(Volume!$B$3:$B$68=$E127),0),MATCH($D127,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="5" t="s">
+      <c r="A128" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B128" s="5" t="s">
+      <c r="B128" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C128" s="5" t="s">
+      <c r="C128" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D128" s="5" t="s">
+      <c r="D128" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E128" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F128" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G128" s="1" t="n">
+      <c r="E128" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G128" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H128" s="6" t="n">
-        <f aca="false" t="array" ref="H128:H128">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B128)*(Volume!$B$3:$B$68=E128),0), MATCH(D128,Volume!$D$2:$F$2,0))</f>
+      <c r="H128" s="7" t="n">
+        <f aca="false" t="array" ref="H128:H128">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B128)*(Volume!$B$3:$B$68=$E128),0),MATCH($D128,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="5" t="s">
+      <c r="A129" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B129" s="5" t="s">
+      <c r="B129" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C129" s="5" t="s">
+      <c r="C129" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D129" s="5" t="s">
+      <c r="D129" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E129" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F129" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G129" s="1" t="n">
+      <c r="E129" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G129" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H129" s="6" t="n">
-        <f aca="false" t="array" ref="H129:H129">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B129)*(Volume!$B$3:$B$68=E129),0), MATCH(D129,Volume!$D$2:$F$2,0))</f>
+      <c r="H129" s="7" t="n">
+        <f aca="false" t="array" ref="H129:H129">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B129)*(Volume!$B$3:$B$68=$E129),0),MATCH($D129,Volume!$D$2:$F$2,0))</f>
         <v>84.5</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="5" t="s">
+      <c r="A130" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B130" s="5" t="s">
+      <c r="B130" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C130" s="5" t="s">
+      <c r="C130" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D130" s="5" t="s">
+      <c r="D130" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E130" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F130" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G130" s="1" t="n">
+      <c r="E130" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G130" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H130" s="6" t="n">
-        <f aca="false" t="array" ref="H130:H130">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B130)*(Volume!$B$3:$B$68=E130),0), MATCH(D130,Volume!$D$2:$F$2,0))</f>
+      <c r="H130" s="7" t="n">
+        <f aca="false" t="array" ref="H130:H130">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B130)*(Volume!$B$3:$B$68=$E130),0),MATCH($D130,Volume!$D$2:$F$2,0))</f>
         <v>56</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="5" t="s">
+      <c r="A131" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B131" s="5" t="s">
+      <c r="B131" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C131" s="5" t="s">
+      <c r="C131" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D131" s="5" t="s">
+      <c r="D131" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E131" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G131" s="1" t="n">
+      <c r="E131" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G131" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="H131" s="6" t="n">
-        <f aca="false" t="array" ref="H131:H131">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B131)*(Volume!$B$3:$B$68=E131),0), MATCH(D131,Volume!$D$2:$F$2,0))</f>
+      <c r="H131" s="7" t="n">
+        <f aca="false" t="array" ref="H131:H131">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B131)*(Volume!$B$3:$B$68=$E131),0),MATCH($D131,Volume!$D$2:$F$2,0))</f>
         <v>17</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="5" t="s">
+      <c r="A132" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B132" s="5" t="s">
+      <c r="B132" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C132" s="5" t="s">
+      <c r="C132" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D132" s="5" t="s">
+      <c r="D132" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E132" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F132" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G132" s="1" t="n">
+      <c r="E132" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G132" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="H132" s="6" t="n">
-        <f aca="false" t="array" ref="H132:H132">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B132)*(Volume!$B$3:$B$68=E132),0), MATCH(D132,Volume!$D$2:$F$2,0))</f>
+      <c r="H132" s="7" t="n">
+        <f aca="false" t="array" ref="H132:H132">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B132)*(Volume!$B$3:$B$68=$E132),0),MATCH($D132,Volume!$D$2:$F$2,0))</f>
         <v>17</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="5" t="s">
+      <c r="A133" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B133" s="5" t="s">
+      <c r="B133" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C133" s="5" t="s">
+      <c r="C133" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D133" s="5" t="s">
+      <c r="D133" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E133" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F133" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G133" s="1" t="n">
+      <c r="E133" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F133" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G133" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H133" s="6" t="n">
-        <f aca="false" t="array" ref="H133:H133">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B133)*(Volume!$B$3:$B$68=E133),0), MATCH(D133,Volume!$D$2:$F$2,0))</f>
+      <c r="H133" s="7" t="n">
+        <f aca="false" t="array" ref="H133:H133">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B133)*(Volume!$B$3:$B$68=$E133),0),MATCH($D133,Volume!$D$2:$F$2,0))</f>
         <v>17.5</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="5" t="s">
+      <c r="A134" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B134" s="5" t="s">
+      <c r="B134" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C134" s="5" t="s">
+      <c r="C134" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D134" s="5" t="s">
+      <c r="D134" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E134" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F134" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G134" s="1" t="n">
+      <c r="E134" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G134" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H134" s="6" t="n">
-        <f aca="false" t="array" ref="H134:H134">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B134)*(Volume!$B$3:$B$68=E134),0), MATCH(D134,Volume!$D$2:$F$2,0))</f>
+      <c r="H134" s="7" t="n">
+        <f aca="false" t="array" ref="H134:H134">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B134)*(Volume!$B$3:$B$68=$E134),0),MATCH($D134,Volume!$D$2:$F$2,0))</f>
         <v>5.5</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="5" t="s">
+      <c r="A135" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B135" s="5" t="s">
+      <c r="B135" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C135" s="5" t="s">
+      <c r="C135" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D135" s="5" t="s">
+      <c r="D135" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E135" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F135" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G135" s="1" t="n">
+      <c r="E135" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F135" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G135" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H135" s="6" t="n">
-        <f aca="false" t="array" ref="H135:H135">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B135)*(Volume!$B$3:$B$68=E135),0), MATCH(D135,Volume!$D$2:$F$2,0))</f>
+      <c r="H135" s="7" t="n">
+        <f aca="false" t="array" ref="H135:H135">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B135)*(Volume!$B$3:$B$68=$E135),0),MATCH($D135,Volume!$D$2:$F$2,0))</f>
         <v>6</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="5" t="s">
+      <c r="A136" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B136" s="5" t="s">
+      <c r="B136" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C136" s="5" t="s">
+      <c r="C136" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D136" s="5" t="s">
+      <c r="D136" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E136" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F136" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G136" s="1" t="n">
+      <c r="E136" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G136" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H136" s="6" t="n">
-        <f aca="false" t="array" ref="H136:H136">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B136)*(Volume!$B$3:$B$68=E136),0), MATCH(D136,Volume!$D$2:$F$2,0))</f>
+      <c r="H136" s="7" t="n">
+        <f aca="false" t="array" ref="H136:H136">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B136)*(Volume!$B$3:$B$68=$E136),0),MATCH($D136,Volume!$D$2:$F$2,0))</f>
         <v>4.5</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="5" t="s">
+      <c r="A137" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B137" s="5" t="s">
+      <c r="B137" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C137" s="5" t="s">
+      <c r="C137" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D137" s="5" t="s">
+      <c r="D137" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E137" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G137" s="1" t="n">
+      <c r="E137" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F137" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G137" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H137" s="6" t="n">
-        <f aca="false" t="array" ref="H137:H137">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B137)*(Volume!$B$3:$B$68=E137),0), MATCH(D137,Volume!$D$2:$F$2,0))</f>
+      <c r="H137" s="7" t="n">
+        <f aca="false" t="array" ref="H137:H137">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B137)*(Volume!$B$3:$B$68=$E137),0),MATCH($D137,Volume!$D$2:$F$2,0))</f>
         <v>12</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="5" t="s">
+      <c r="A138" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B138" s="5" t="s">
+      <c r="B138" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C138" s="5" t="s">
+      <c r="C138" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D138" s="5" t="s">
+      <c r="D138" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E138" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G138" s="1" t="n">
+      <c r="E138" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F138" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G138" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H138" s="6" t="n">
-        <f aca="false" t="array" ref="H138:H138">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B138)*(Volume!$B$3:$B$68=E138),0), MATCH(D138,Volume!$D$2:$F$2,0))</f>
+      <c r="H138" s="7" t="n">
+        <f aca="false" t="array" ref="H138:H138">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B138)*(Volume!$B$3:$B$68=$E138),0),MATCH($D138,Volume!$D$2:$F$2,0))</f>
         <v>3.5</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="5" t="s">
+      <c r="A139" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B139" s="5" t="s">
+      <c r="B139" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C139" s="5" t="s">
+      <c r="C139" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D139" s="5" t="s">
+      <c r="D139" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E139" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G139" s="1" t="n">
+      <c r="E139" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F139" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G139" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H139" s="6" t="n">
-        <f aca="false" t="array" ref="H139:H139">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B139)*(Volume!$B$3:$B$68=E139),0), MATCH(D139,Volume!$D$2:$F$2,0))</f>
+      <c r="H139" s="7" t="n">
+        <f aca="false" t="array" ref="H139:H139">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B139)*(Volume!$B$3:$B$68=$E139),0),MATCH($D139,Volume!$D$2:$F$2,0))</f>
         <v>4</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="5" t="s">
+      <c r="A140" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B140" s="5" t="s">
+      <c r="B140" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C140" s="5" t="s">
+      <c r="C140" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D140" s="5" t="s">
+      <c r="D140" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E140" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G140" s="1" t="n">
+      <c r="E140" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G140" s="2" t="n">
         <v>575</v>
       </c>
-      <c r="H140" s="6" t="n">
-        <f aca="false" t="array" ref="H140:H140">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B140)*(Volume!$B$3:$B$68=E140),0), MATCH(D140,Volume!$D$2:$F$2,0))</f>
+      <c r="H140" s="7" t="n">
+        <f aca="false" t="array" ref="H140:H140">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B140)*(Volume!$B$3:$B$68=$E140),0),MATCH($D140,Volume!$D$2:$F$2,0))</f>
         <v>3.5</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="5" t="s">
+      <c r="A141" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B141" s="5" t="s">
+      <c r="B141" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C141" s="5" t="s">
+      <c r="C141" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D141" s="5" t="s">
+      <c r="D141" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E141" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G141" s="1" t="n">
+      <c r="E141" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F141" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G141" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="H141" s="6" t="n">
-        <f aca="false" t="array" ref="H141:H141">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B141)*(Volume!$B$3:$B$68=E141),0), MATCH(D141,Volume!$D$2:$F$2,0))</f>
+      <c r="H141" s="7" t="n">
+        <f aca="false" t="array" ref="H141:H141">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B141)*(Volume!$B$3:$B$68=$E141),0),MATCH($D141,Volume!$D$2:$F$2,0))</f>
         <v>2.5</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="5" t="s">
+      <c r="A142" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B142" s="5" t="s">
+      <c r="B142" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C142" s="5" t="s">
+      <c r="C142" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D142" s="5" t="s">
+      <c r="D142" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E142" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G142" s="1" t="n">
+      <c r="E142" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G142" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H142" s="6" t="n">
-        <f aca="false" t="array" ref="H142:H142">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B142)*(Volume!$B$3:$B$68=E142),0), MATCH(D142,Volume!$D$2:$F$2,0))</f>
+      <c r="H142" s="7" t="n">
+        <f aca="false" t="array" ref="H142:H142">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B142)*(Volume!$B$3:$B$68=$E142),0),MATCH($D142,Volume!$D$2:$F$2,0))</f>
         <v>2.5</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="5" t="s">
+      <c r="A143" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B143" s="5" t="s">
+      <c r="B143" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C143" s="5" t="s">
+      <c r="C143" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D143" s="5" t="s">
+      <c r="D143" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E143" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G143" s="1" t="n">
+      <c r="E143" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F143" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G143" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H143" s="6" t="n">
-        <f aca="false" t="array" ref="H143:H143">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B143)*(Volume!$B$3:$B$68=E143),0), MATCH(D143,Volume!$D$2:$F$2,0))</f>
+      <c r="H143" s="7" t="n">
+        <f aca="false" t="array" ref="H143:H143">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B143)*(Volume!$B$3:$B$68=$E143),0),MATCH($D143,Volume!$D$2:$F$2,0))</f>
         <v>3</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="5" t="s">
+      <c r="A144" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B144" s="5" t="s">
+      <c r="B144" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C144" s="5" t="s">
+      <c r="C144" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D144" s="5" t="s">
+      <c r="D144" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E144" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G144" s="1" t="n">
+      <c r="E144" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G144" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="H144" s="6" t="n">
-        <f aca="false" t="array" ref="H144:H144">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B144)*(Volume!$B$3:$B$68=E144),0), MATCH(D144,Volume!$D$2:$F$2,0))</f>
+      <c r="H144" s="7" t="n">
+        <f aca="false" t="array" ref="H144:H144">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B144)*(Volume!$B$3:$B$68=$E144),0),MATCH($D144,Volume!$D$2:$F$2,0))</f>
         <v>2.5</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="5" t="s">
+      <c r="A145" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B145" s="5" t="s">
+      <c r="B145" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C145" s="5" t="s">
+      <c r="C145" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D145" s="5" t="s">
+      <c r="D145" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E145" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G145" s="1" t="n">
+      <c r="E145" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F145" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G145" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H145" s="6" t="n">
-        <f aca="false" t="array" ref="H145:H145">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B145)*(Volume!$B$3:$B$68=E145),0), MATCH(D145,Volume!$D$2:$F$2,0))</f>
+      <c r="H145" s="7" t="n">
+        <f aca="false" t="array" ref="H145:H145">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B145)*(Volume!$B$3:$B$68=$E145),0),MATCH($D145,Volume!$D$2:$F$2,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="5" t="s">
+      <c r="A146" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B146" s="5" t="s">
+      <c r="B146" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C146" s="5" t="s">
+      <c r="C146" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D146" s="5" t="s">
+      <c r="D146" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E146" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G146" s="1" t="n">
+      <c r="E146" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G146" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H146" s="6" t="n">
-        <f aca="false" t="array" ref="H146:H146">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B146)*(Volume!$B$3:$B$68=E146),0), MATCH(D146,Volume!$D$2:$F$2,0))</f>
+      <c r="H146" s="7" t="n">
+        <f aca="false" t="array" ref="H146:H146">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B146)*(Volume!$B$3:$B$68=$E146),0),MATCH($D146,Volume!$D$2:$F$2,0))</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="5" t="s">
+      <c r="A147" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B147" s="5" t="s">
+      <c r="B147" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C147" s="5" t="s">
+      <c r="C147" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D147" s="5" t="s">
+      <c r="D147" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E147" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G147" s="1" t="n">
+      <c r="E147" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G147" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H147" s="6" t="n">
-        <f aca="false" t="array" ref="H147:H147">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B147)*(Volume!$B$3:$B$68=E147),0), MATCH(D147,Volume!$D$2:$F$2,0))</f>
+      <c r="H147" s="7" t="n">
+        <f aca="false" t="array" ref="H147:H147">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B147)*(Volume!$B$3:$B$68=$E147),0),MATCH($D147,Volume!$D$2:$F$2,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="5" t="s">
+      <c r="A148" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B148" s="5" t="s">
+      <c r="B148" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C148" s="5" t="s">
+      <c r="C148" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D148" s="5" t="s">
+      <c r="D148" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E148" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G148" s="1" t="n">
+      <c r="E148" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F148" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G148" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H148" s="6" t="n">
-        <f aca="false" t="array" ref="H148:H148">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B148)*(Volume!$B$3:$B$68=E148),0), MATCH(D148,Volume!$D$2:$F$2,0))</f>
+      <c r="H148" s="7" t="n">
+        <f aca="false" t="array" ref="H148:H148">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B148)*(Volume!$B$3:$B$68=$E148),0),MATCH($D148,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="5" t="s">
+      <c r="A149" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B149" s="5" t="s">
+      <c r="B149" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C149" s="5" t="s">
+      <c r="C149" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D149" s="5" t="s">
+      <c r="D149" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E149" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G149" s="1" t="n">
+      <c r="E149" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F149" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G149" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H149" s="6" t="n">
-        <f aca="false" t="array" ref="H149:H149">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B149)*(Volume!$B$3:$B$68=E149),0), MATCH(D149,Volume!$D$2:$F$2,0))</f>
+      <c r="H149" s="7" t="n">
+        <f aca="false" t="array" ref="H149:H149">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B149)*(Volume!$B$3:$B$68=$E149),0),MATCH($D149,Volume!$D$2:$F$2,0))</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="5" t="s">
+      <c r="A150" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B150" s="5" t="s">
+      <c r="B150" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C150" s="5" t="s">
+      <c r="C150" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D150" s="5" t="s">
+      <c r="D150" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E150" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G150" s="1" t="n">
+      <c r="E150" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G150" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H150" s="6" t="n">
-        <f aca="false" t="array" ref="H150:H150">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B150)*(Volume!$B$3:$B$68=E150),0), MATCH(D150,Volume!$D$2:$F$2,0))</f>
+      <c r="H150" s="7" t="n">
+        <f aca="false" t="array" ref="H150:H150">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B150)*(Volume!$B$3:$B$68=$E150),0),MATCH($D150,Volume!$D$2:$F$2,0))</f>
         <v>120</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="5" t="s">
+      <c r="A151" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B151" s="5" t="s">
+      <c r="B151" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C151" s="5" t="s">
+      <c r="C151" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D151" s="5" t="s">
+      <c r="D151" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E151" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G151" s="1" t="n">
+      <c r="E151" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G151" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H151" s="6" t="n">
-        <f aca="false" t="array" ref="H151:H151">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B151)*(Volume!$B$3:$B$68=E151),0), MATCH(D151,Volume!$D$2:$F$2,0))</f>
+      <c r="H151" s="7" t="n">
+        <f aca="false" t="array" ref="H151:H151">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B151)*(Volume!$B$3:$B$68=$E151),0),MATCH($D151,Volume!$D$2:$F$2,0))</f>
         <v>66</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="5" t="s">
+      <c r="A152" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B152" s="5" t="s">
+      <c r="B152" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C152" s="5" t="s">
+      <c r="C152" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D152" s="5" t="s">
+      <c r="D152" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E152" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F152" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G152" s="1" t="n">
+      <c r="E152" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G152" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H152" s="6" t="n">
-        <f aca="false" t="array" ref="H152:H152">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B152)*(Volume!$B$3:$B$68=E152),0), MATCH(D152,Volume!$D$2:$F$2,0))</f>
+      <c r="H152" s="7" t="n">
+        <f aca="false" t="array" ref="H152:H152">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B152)*(Volume!$B$3:$B$68=$E152),0),MATCH($D152,Volume!$D$2:$F$2,0))</f>
         <v>18</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="5" t="s">
+      <c r="A153" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B153" s="5" t="s">
+      <c r="B153" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="5" t="s">
+      <c r="C153" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D153" s="5" t="s">
+      <c r="D153" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E153" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F153" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G153" s="1" t="n">
+      <c r="E153" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G153" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H153" s="6" t="n">
-        <f aca="false" t="array" ref="H153:H153">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B153)*(Volume!$B$3:$B$68=E153),0), MATCH(D153,Volume!$D$2:$F$2,0))</f>
+      <c r="H153" s="7" t="n">
+        <f aca="false" t="array" ref="H153:H153">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B153)*(Volume!$B$3:$B$68=$E153),0),MATCH($D153,Volume!$D$2:$F$2,0))</f>
         <v>4.5</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="5" t="s">
+      <c r="A154" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B154" s="5" t="s">
+      <c r="B154" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C154" s="5" t="s">
+      <c r="C154" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D154" s="5" t="s">
+      <c r="D154" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E154" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G154" s="1" t="n">
+      <c r="E154" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G154" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H154" s="6" t="n">
-        <f aca="false" t="array" ref="H154:H154">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B154)*(Volume!$B$3:$B$68=E154),0), MATCH(D154,Volume!$D$2:$F$2,0))</f>
+      <c r="H154" s="7" t="n">
+        <f aca="false" t="array" ref="H154:H154">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B154)*(Volume!$B$3:$B$68=$E154),0),MATCH($D154,Volume!$D$2:$F$2,0))</f>
         <v>17</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="5" t="s">
+      <c r="A155" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B155" s="5" t="s">
+      <c r="B155" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C155" s="5" t="s">
+      <c r="C155" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D155" s="5" t="s">
+      <c r="D155" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E155" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F155" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G155" s="1" t="n">
+      <c r="E155" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F155" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G155" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H155" s="6" t="n">
-        <f aca="false" t="array" ref="H155:H155">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B155)*(Volume!$B$3:$B$68=E155),0), MATCH(D155,Volume!$D$2:$F$2,0))</f>
+      <c r="H155" s="7" t="n">
+        <f aca="false" t="array" ref="H155:H155">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B155)*(Volume!$B$3:$B$68=$E155),0),MATCH($D155,Volume!$D$2:$F$2,0))</f>
         <v>11</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="5" t="s">
+      <c r="A156" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B156" s="5" t="s">
+      <c r="B156" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C156" s="5" t="s">
+      <c r="C156" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D156" s="5" t="s">
+      <c r="D156" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E156" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F156" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G156" s="1" t="n">
+      <c r="E156" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G156" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="H156" s="6" t="n">
-        <f aca="false" t="array" ref="H156:H156">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B156)*(Volume!$B$3:$B$68=E156),0), MATCH(D156,Volume!$D$2:$F$2,0))</f>
+      <c r="H156" s="7" t="n">
+        <f aca="false" t="array" ref="H156:H156">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B156)*(Volume!$B$3:$B$68=$E156),0),MATCH($D156,Volume!$D$2:$F$2,0))</f>
         <v>5.5</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="5" t="s">
+      <c r="A157" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B157" s="5" t="s">
+      <c r="B157" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C157" s="5" t="s">
+      <c r="C157" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D157" s="5" t="s">
+      <c r="D157" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E157" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G157" s="1" t="n">
+      <c r="E157" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F157" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G157" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H157" s="6" t="n">
-        <f aca="false" t="array" ref="H157:H157">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B157)*(Volume!$B$3:$B$68=E157),0), MATCH(D157,Volume!$D$2:$F$2,0))</f>
+      <c r="H157" s="7" t="n">
+        <f aca="false" t="array" ref="H157:H157">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B157)*(Volume!$B$3:$B$68=$E157),0),MATCH($D157,Volume!$D$2:$F$2,0))</f>
         <v>7.5</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="5" t="s">
+      <c r="A158" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B158" s="5" t="s">
+      <c r="B158" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C158" s="5" t="s">
+      <c r="C158" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D158" s="5" t="s">
+      <c r="D158" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E158" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F158" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G158" s="1" t="n">
+      <c r="E158" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G158" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H158" s="6" t="n">
-        <f aca="false" t="array" ref="H158:H158">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B158)*(Volume!$B$3:$B$68=E158),0), MATCH(D158,Volume!$D$2:$F$2,0))</f>
+      <c r="H158" s="7" t="n">
+        <f aca="false" t="array" ref="H158:H158">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B158)*(Volume!$B$3:$B$68=$E158),0),MATCH($D158,Volume!$D$2:$F$2,0))</f>
         <v>3</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="5" t="s">
+      <c r="A159" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B159" s="5" t="s">
+      <c r="B159" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C159" s="5" t="s">
+      <c r="C159" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D159" s="5" t="s">
+      <c r="D159" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E159" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G159" s="1" t="n">
+      <c r="E159" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F159" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G159" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H159" s="6" t="n">
-        <f aca="false" t="array" ref="H159:H159">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B159)*(Volume!$B$3:$B$68=E159),0), MATCH(D159,Volume!$D$2:$F$2,0))</f>
+      <c r="H159" s="7" t="n">
+        <f aca="false" t="array" ref="H159:H159">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B159)*(Volume!$B$3:$B$68=$E159),0),MATCH($D159,Volume!$D$2:$F$2,0))</f>
         <v>6</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="5" t="s">
+      <c r="A160" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B160" s="5" t="s">
+      <c r="B160" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C160" s="5" t="s">
+      <c r="C160" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D160" s="5" t="s">
+      <c r="D160" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E160" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F160" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G160" s="1" t="n">
+      <c r="E160" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F160" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G160" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H160" s="6" t="n">
-        <f aca="false" t="array" ref="H160:H160">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B160)*(Volume!$B$3:$B$68=E160),0), MATCH(D160,Volume!$D$2:$F$2,0))</f>
+      <c r="H160" s="7" t="n">
+        <f aca="false" t="array" ref="H160:H160">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B160)*(Volume!$B$3:$B$68=$E160),0),MATCH($D160,Volume!$D$2:$F$2,0))</f>
         <v>4</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="5" t="s">
+      <c r="A161" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B161" s="5" t="s">
+      <c r="B161" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C161" s="5" t="s">
+      <c r="C161" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D161" s="5" t="s">
+      <c r="D161" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E161" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F161" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G161" s="1" t="n">
+      <c r="E161" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F161" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G161" s="2" t="n">
         <v>975</v>
       </c>
-      <c r="H161" s="6" t="n">
-        <f aca="false" t="array" ref="H161:H161">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B161)*(Volume!$B$3:$B$68=E161),0), MATCH(D161,Volume!$D$2:$F$2,0))</f>
+      <c r="H161" s="7" t="n">
+        <f aca="false" t="array" ref="H161:H161">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B161)*(Volume!$B$3:$B$68=$E161),0),MATCH($D161,Volume!$D$2:$F$2,0))</f>
         <v>5</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="5" t="s">
+      <c r="A162" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B162" s="5" t="s">
+      <c r="B162" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C162" s="5" t="s">
+      <c r="C162" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D162" s="5" t="s">
+      <c r="D162" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E162" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F162" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G162" s="1" t="n">
+      <c r="E162" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F162" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G162" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="H162" s="6" t="n">
-        <f aca="false" t="array" ref="H162:H162">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B162)*(Volume!$B$3:$B$68=E162),0), MATCH(D162,Volume!$D$2:$F$2,0))</f>
+      <c r="H162" s="7" t="n">
+        <f aca="false" t="array" ref="H162:H162">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B162)*(Volume!$B$3:$B$68=$E162),0),MATCH($D162,Volume!$D$2:$F$2,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="5" t="s">
+      <c r="A163" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B163" s="5" t="s">
+      <c r="B163" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C163" s="5" t="s">
+      <c r="C163" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D163" s="5" t="s">
+      <c r="D163" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E163" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G163" s="1" t="n">
+      <c r="E163" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G163" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="H163" s="6" t="n">
-        <f aca="false" t="array" ref="H163:H163">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B163)*(Volume!$B$3:$B$68=E163),0), MATCH(D163,Volume!$D$2:$F$2,0))</f>
+      <c r="H163" s="7" t="n">
+        <f aca="false" t="array" ref="H163:H163">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B163)*(Volume!$B$3:$B$68=$E163),0),MATCH($D163,Volume!$D$2:$F$2,0))</f>
         <v>3.5</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="5" t="s">
+      <c r="A164" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B164" s="5" t="s">
+      <c r="B164" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C164" s="5" t="s">
+      <c r="C164" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D164" s="5" t="s">
+      <c r="D164" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E164" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F164" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G164" s="1" t="n">
+      <c r="E164" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F164" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H164" s="6" t="n">
-        <f aca="false" t="array" ref="H164:H164">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B164)*(Volume!$B$3:$B$68=E164),0), MATCH(D164,Volume!$D$2:$F$2,0))</f>
+      <c r="H164" s="7" t="n">
+        <f aca="false" t="array" ref="H164:H164">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B164)*(Volume!$B$3:$B$68=$E164),0),MATCH($D164,Volume!$D$2:$F$2,0))</f>
         <v>1.5</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="5" t="s">
+      <c r="A165" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B165" s="5" t="s">
+      <c r="B165" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C165" s="5" t="s">
+      <c r="C165" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D165" s="5" t="s">
+      <c r="D165" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E165" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F165" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G165" s="1" t="n">
+      <c r="E165" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F165" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G165" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H165" s="6" t="n">
-        <f aca="false" t="array" ref="H165:H165">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B165)*(Volume!$B$3:$B$68=E165),0), MATCH(D165,Volume!$D$2:$F$2,0))</f>
+      <c r="H165" s="7" t="n">
+        <f aca="false" t="array" ref="H165:H165">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B165)*(Volume!$B$3:$B$68=$E165),0),MATCH($D165,Volume!$D$2:$F$2,0))</f>
         <v>1.5</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="5" t="s">
+      <c r="A166" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B166" s="5" t="s">
+      <c r="B166" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C166" s="5" t="s">
+      <c r="C166" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D166" s="5" t="s">
+      <c r="D166" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E166" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G166" s="1" t="n">
+      <c r="E166" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F166" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G166" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="H166" s="6" t="n">
-        <f aca="false" t="array" ref="H166:H166">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B166)*(Volume!$B$3:$B$68=E166),0), MATCH(D166,Volume!$D$2:$F$2,0))</f>
+      <c r="H166" s="7" t="n">
+        <f aca="false" t="array" ref="H166:H166">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B166)*(Volume!$B$3:$B$68=$E166),0),MATCH($D166,Volume!$D$2:$F$2,0))</f>
         <v>2</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="5" t="s">
+      <c r="A167" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B167" s="5" t="s">
+      <c r="B167" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C167" s="5" t="s">
+      <c r="C167" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D167" s="5" t="s">
+      <c r="D167" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E167" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G167" s="1" t="n">
+      <c r="E167" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F167" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G167" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H167" s="6" t="n">
-        <f aca="false" t="array" ref="H167:H167">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B167)*(Volume!$B$3:$B$68=E167),0), MATCH(D167,Volume!$D$2:$F$2,0))</f>
+      <c r="H167" s="7" t="n">
+        <f aca="false" t="array" ref="H167:H167">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B167)*(Volume!$B$3:$B$68=$E167),0),MATCH($D167,Volume!$D$2:$F$2,0))</f>
         <v>1.5</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="5" t="s">
+      <c r="A168" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B168" s="5" t="s">
+      <c r="B168" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C168" s="5" t="s">
+      <c r="C168" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D168" s="5" t="s">
+      <c r="D168" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E168" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G168" s="1" t="n">
+      <c r="E168" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F168" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G168" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H168" s="6" t="n">
-        <f aca="false" t="array" ref="H168:H168">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B168)*(Volume!$B$3:$B$68=E168),0), MATCH(D168,Volume!$D$2:$F$2,0))</f>
+      <c r="H168" s="7" t="n">
+        <f aca="false" t="array" ref="H168:H168">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B168)*(Volume!$B$3:$B$68=$E168),0),MATCH($D168,Volume!$D$2:$F$2,0))</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="5" t="s">
+      <c r="A169" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B169" s="5" t="s">
+      <c r="B169" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C169" s="5" t="s">
+      <c r="C169" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D169" s="5" t="s">
+      <c r="D169" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E169" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G169" s="1" t="n">
+      <c r="E169" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F169" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G169" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H169" s="6" t="n">
-        <f aca="false" t="array" ref="H169:H169">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B169)*(Volume!$B$3:$B$68=E169),0), MATCH(D169,Volume!$D$2:$F$2,0))</f>
+      <c r="H169" s="7" t="n">
+        <f aca="false" t="array" ref="H169:H169">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B169)*(Volume!$B$3:$B$68=$E169),0),MATCH($D169,Volume!$D$2:$F$2,0))</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="5" t="s">
+      <c r="A170" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B170" s="5" t="s">
+      <c r="B170" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C170" s="5" t="s">
+      <c r="C170" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D170" s="5" t="s">
+      <c r="D170" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E170" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G170" s="1" t="n">
+      <c r="E170" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F170" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G170" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H170" s="6" t="n">
-        <f aca="false" t="array" ref="H170:H170">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B170)*(Volume!$B$3:$B$68=E170),0), MATCH(D170,Volume!$D$2:$F$2,0))</f>
+      <c r="H170" s="7" t="n">
+        <f aca="false" t="array" ref="H170:H170">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B170)*(Volume!$B$3:$B$68=$E170),0),MATCH($D170,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="5" t="s">
+      <c r="A171" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B171" s="5" t="s">
+      <c r="B171" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C171" s="5" t="s">
+      <c r="C171" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D171" s="5" t="s">
+      <c r="D171" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E171" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G171" s="1" t="n">
+      <c r="E171" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F171" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G171" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H171" s="6" t="n">
-        <f aca="false" t="array" ref="H171:H171">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B171)*(Volume!$B$3:$B$68=E171),0), MATCH(D171,Volume!$D$2:$F$2,0))</f>
+      <c r="H171" s="7" t="n">
+        <f aca="false" t="array" ref="H171:H171">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B171)*(Volume!$B$3:$B$68=$E171),0),MATCH($D171,Volume!$D$2:$F$2,0))</f>
         <v>86.5</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="5" t="s">
+      <c r="A172" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B172" s="5" t="s">
+      <c r="B172" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C172" s="5" t="s">
+      <c r="C172" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D172" s="5" t="s">
+      <c r="D172" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E172" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G172" s="1" t="n">
+      <c r="E172" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F172" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G172" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H172" s="6" t="n">
-        <f aca="false" t="array" ref="H172:H172">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B172)*(Volume!$B$3:$B$68=E172),0), MATCH(D172,Volume!$D$2:$F$2,0))</f>
+      <c r="H172" s="7" t="n">
+        <f aca="false" t="array" ref="H172:H172">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B172)*(Volume!$B$3:$B$68=$E172),0),MATCH($D172,Volume!$D$2:$F$2,0))</f>
         <v>72.5</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="5" t="s">
+      <c r="A173" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B173" s="5" t="s">
+      <c r="B173" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C173" s="5" t="s">
+      <c r="C173" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D173" s="5" t="s">
+      <c r="D173" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E173" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G173" s="1" t="n">
+      <c r="E173" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F173" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G173" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H173" s="6" t="n">
-        <f aca="false" t="array" ref="H173:H173">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B173)*(Volume!$B$3:$B$68=E173),0), MATCH(D173,Volume!$D$2:$F$2,0))</f>
+      <c r="H173" s="7" t="n">
+        <f aca="false" t="array" ref="H173:H173">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B173)*(Volume!$B$3:$B$68=$E173),0),MATCH($D173,Volume!$D$2:$F$2,0))</f>
         <v>14.5</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="5" t="s">
+      <c r="A174" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B174" s="5" t="s">
+      <c r="B174" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C174" s="5" t="s">
+      <c r="C174" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D174" s="5" t="s">
+      <c r="D174" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E174" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G174" s="1" t="n">
+      <c r="E174" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F174" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G174" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H174" s="6" t="n">
-        <f aca="false" t="array" ref="H174:H174">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B174)*(Volume!$B$3:$B$68=E174),0), MATCH(D174,Volume!$D$2:$F$2,0))</f>
+      <c r="H174" s="7" t="n">
+        <f aca="false" t="array" ref="H174:H174">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B174)*(Volume!$B$3:$B$68=$E174),0),MATCH($D174,Volume!$D$2:$F$2,0))</f>
         <v>22.5</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="5" t="s">
+      <c r="A175" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B175" s="5" t="s">
+      <c r="B175" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C175" s="5" t="s">
+      <c r="C175" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D175" s="5" t="s">
+      <c r="D175" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E175" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G175" s="1" t="n">
+      <c r="E175" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F175" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G175" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H175" s="6" t="n">
-        <f aca="false" t="array" ref="H175:H175">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B175)*(Volume!$B$3:$B$68=E175),0), MATCH(D175,Volume!$D$2:$F$2,0))</f>
+      <c r="H175" s="7" t="n">
+        <f aca="false" t="array" ref="H175:H175">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B175)*(Volume!$B$3:$B$68=$E175),0),MATCH($D175,Volume!$D$2:$F$2,0))</f>
         <v>9</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="5" t="s">
+      <c r="A176" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B176" s="5" t="s">
+      <c r="B176" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C176" s="5" t="s">
+      <c r="C176" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D176" s="5" t="s">
+      <c r="D176" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E176" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G176" s="1" t="n">
+      <c r="E176" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F176" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G176" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H176" s="6" t="n">
-        <f aca="false" t="array" ref="H176:H176">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B176)*(Volume!$B$3:$B$68=E176),0), MATCH(D176,Volume!$D$2:$F$2,0))</f>
+      <c r="H176" s="7" t="n">
+        <f aca="false" t="array" ref="H176:H176">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B176)*(Volume!$B$3:$B$68=$E176),0),MATCH($D176,Volume!$D$2:$F$2,0))</f>
         <v>3.5</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="5" t="s">
+      <c r="A177" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B177" s="5" t="s">
+      <c r="B177" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C177" s="5" t="s">
+      <c r="C177" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D177" s="5" t="s">
+      <c r="D177" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E177" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G177" s="1" t="n">
+      <c r="E177" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F177" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G177" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="H177" s="6" t="n">
-        <f aca="false" t="array" ref="H177:H177">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B177)*(Volume!$B$3:$B$68=E177),0), MATCH(D177,Volume!$D$2:$F$2,0))</f>
+      <c r="H177" s="7" t="n">
+        <f aca="false" t="array" ref="H177:H177">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B177)*(Volume!$B$3:$B$68=$E177),0),MATCH($D177,Volume!$D$2:$F$2,0))</f>
         <v>5</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="5" t="s">
+      <c r="A178" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B178" s="5" t="s">
+      <c r="B178" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C178" s="5" t="s">
+      <c r="C178" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D178" s="5" t="s">
+      <c r="D178" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E178" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G178" s="1" t="n">
+      <c r="E178" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F178" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G178" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H178" s="6" t="n">
-        <f aca="false" t="array" ref="H178:H178">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B178)*(Volume!$B$3:$B$68=E178),0), MATCH(D178,Volume!$D$2:$F$2,0))</f>
+      <c r="H178" s="7" t="n">
+        <f aca="false" t="array" ref="H178:H178">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B178)*(Volume!$B$3:$B$68=$E178),0),MATCH($D178,Volume!$D$2:$F$2,0))</f>
         <v>3.5</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="5" t="s">
+      <c r="A179" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B179" s="5" t="s">
+      <c r="B179" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C179" s="5" t="s">
+      <c r="C179" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D179" s="5" t="s">
+      <c r="D179" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E179" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G179" s="1" t="n">
+      <c r="E179" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F179" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G179" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H179" s="6" t="n">
-        <f aca="false" t="array" ref="H179:H179">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B179)*(Volume!$B$3:$B$68=E179),0), MATCH(D179,Volume!$D$2:$F$2,0))</f>
+      <c r="H179" s="7" t="n">
+        <f aca="false" t="array" ref="H179:H179">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B179)*(Volume!$B$3:$B$68=$E179),0),MATCH($D179,Volume!$D$2:$F$2,0))</f>
         <v>2.5</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="5" t="s">
+      <c r="A180" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B180" s="5" t="s">
+      <c r="B180" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C180" s="5" t="s">
+      <c r="C180" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D180" s="5" t="s">
+      <c r="D180" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E180" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F180" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G180" s="1" t="n">
+      <c r="E180" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F180" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G180" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H180" s="6" t="n">
-        <f aca="false" t="array" ref="H180:H180">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B180)*(Volume!$B$3:$B$68=E180),0), MATCH(D180,Volume!$D$2:$F$2,0))</f>
+      <c r="H180" s="7" t="n">
+        <f aca="false" t="array" ref="H180:H180">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B180)*(Volume!$B$3:$B$68=$E180),0),MATCH($D180,Volume!$D$2:$F$2,0))</f>
         <v>3</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="5" t="s">
+      <c r="A181" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B181" s="5" t="s">
+      <c r="B181" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C181" s="5" t="s">
+      <c r="C181" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D181" s="5" t="s">
+      <c r="D181" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E181" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F181" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G181" s="1" t="n">
+      <c r="E181" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F181" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G181" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H181" s="6" t="n">
-        <f aca="false" t="array" ref="H181:H181">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B181)*(Volume!$B$3:$B$68=E181),0), MATCH(D181,Volume!$D$2:$F$2,0))</f>
+      <c r="H181" s="7" t="n">
+        <f aca="false" t="array" ref="H181:H181">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B181)*(Volume!$B$3:$B$68=$E181),0),MATCH($D181,Volume!$D$2:$F$2,0))</f>
         <v>4.5</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="5" t="s">
+      <c r="A182" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B182" s="5" t="s">
+      <c r="B182" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C182" s="5" t="s">
+      <c r="C182" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D182" s="5" t="s">
+      <c r="D182" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E182" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G182" s="1" t="n">
+      <c r="E182" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F182" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G182" s="2" t="n">
         <v>975</v>
       </c>
-      <c r="H182" s="6" t="n">
-        <f aca="false" t="array" ref="H182:H182">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B182)*(Volume!$B$3:$B$68=E182),0), MATCH(D182,Volume!$D$2:$F$2,0))</f>
+      <c r="H182" s="7" t="n">
+        <f aca="false" t="array" ref="H182:H182">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B182)*(Volume!$B$3:$B$68=$E182),0),MATCH($D182,Volume!$D$2:$F$2,0))</f>
         <v>2</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="5" t="s">
+      <c r="A183" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B183" s="5" t="s">
+      <c r="B183" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C183" s="5" t="s">
+      <c r="C183" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D183" s="5" t="s">
+      <c r="D183" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E183" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G183" s="1" t="n">
+      <c r="E183" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F183" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G183" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="H183" s="6" t="n">
-        <f aca="false" t="array" ref="H183:H183">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B183)*(Volume!$B$3:$B$68=E183),0), MATCH(D183,Volume!$D$2:$F$2,0))</f>
+      <c r="H183" s="7" t="n">
+        <f aca="false" t="array" ref="H183:H183">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B183)*(Volume!$B$3:$B$68=$E183),0),MATCH($D183,Volume!$D$2:$F$2,0))</f>
         <v>3</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="5" t="s">
+      <c r="A184" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B184" s="5" t="s">
+      <c r="B184" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C184" s="5" t="s">
+      <c r="C184" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D184" s="5" t="s">
+      <c r="D184" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E184" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G184" s="1" t="n">
+      <c r="E184" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F184" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G184" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="H184" s="6" t="n">
-        <f aca="false" t="array" ref="H184:H184">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B184)*(Volume!$B$3:$B$68=E184),0), MATCH(D184,Volume!$D$2:$F$2,0))</f>
+      <c r="H184" s="7" t="n">
+        <f aca="false" t="array" ref="H184:H184">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B184)*(Volume!$B$3:$B$68=$E184),0),MATCH($D184,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="5" t="s">
+      <c r="A185" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B185" s="5" t="s">
+      <c r="B185" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C185" s="5" t="s">
+      <c r="C185" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D185" s="5" t="s">
+      <c r="D185" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E185" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F185" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G185" s="1" t="n">
+      <c r="E185" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F185" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G185" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H185" s="6" t="n">
-        <f aca="false" t="array" ref="H185:H185">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B185)*(Volume!$B$3:$B$68=E185),0), MATCH(D185,Volume!$D$2:$F$2,0))</f>
+      <c r="H185" s="7" t="n">
+        <f aca="false" t="array" ref="H185:H185">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B185)*(Volume!$B$3:$B$68=$E185),0),MATCH($D185,Volume!$D$2:$F$2,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="5" t="s">
+      <c r="A186" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B186" s="5" t="s">
+      <c r="B186" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C186" s="5" t="s">
+      <c r="C186" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D186" s="5" t="s">
+      <c r="D186" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E186" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G186" s="1" t="n">
+      <c r="E186" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F186" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G186" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="H186" s="6" t="n">
-        <f aca="false" t="array" ref="H186:H186">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B186)*(Volume!$B$3:$B$68=E186),0), MATCH(D186,Volume!$D$2:$F$2,0))</f>
+      <c r="H186" s="7" t="n">
+        <f aca="false" t="array" ref="H186:H186">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B186)*(Volume!$B$3:$B$68=$E186),0),MATCH($D186,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="5" t="s">
+      <c r="A187" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B187" s="5" t="s">
+      <c r="B187" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C187" s="5" t="s">
+      <c r="C187" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D187" s="5" t="s">
+      <c r="D187" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E187" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F187" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G187" s="1" t="n">
+      <c r="E187" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F187" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G187" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="H187" s="6" t="n">
-        <f aca="false" t="array" ref="H187:H187">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B187)*(Volume!$B$3:$B$68=E187),0), MATCH(D187,Volume!$D$2:$F$2,0))</f>
+      <c r="H187" s="7" t="n">
+        <f aca="false" t="array" ref="H187:H187">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B187)*(Volume!$B$3:$B$68=$E187),0),MATCH($D187,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="5" t="s">
+      <c r="A188" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B188" s="5" t="s">
+      <c r="B188" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C188" s="5" t="s">
+      <c r="C188" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D188" s="5" t="s">
+      <c r="D188" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E188" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F188" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G188" s="1" t="n">
+      <c r="E188" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F188" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G188" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H188" s="6" t="n">
-        <f aca="false" t="array" ref="H188:H188">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B188)*(Volume!$B$3:$B$68=E188),0), MATCH(D188,Volume!$D$2:$F$2,0))</f>
+      <c r="H188" s="7" t="n">
+        <f aca="false" t="array" ref="H188:H188">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B188)*(Volume!$B$3:$B$68=$E188),0),MATCH($D188,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="5" t="s">
+      <c r="A189" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B189" s="5" t="s">
+      <c r="B189" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C189" s="5" t="s">
+      <c r="C189" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D189" s="5" t="s">
+      <c r="D189" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E189" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F189" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G189" s="1" t="n">
+      <c r="E189" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F189" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G189" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H189" s="6" t="n">
-        <f aca="false" t="array" ref="H189:H189">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B189)*(Volume!$B$3:$B$68=E189),0), MATCH(D189,Volume!$D$2:$F$2,0))</f>
+      <c r="H189" s="7" t="n">
+        <f aca="false" t="array" ref="H189:H189">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B189)*(Volume!$B$3:$B$68=$E189),0),MATCH($D189,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="5" t="s">
+      <c r="A190" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B190" s="5" t="s">
+      <c r="B190" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C190" s="5" t="s">
+      <c r="C190" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D190" s="5" t="s">
+      <c r="D190" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E190" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F190" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G190" s="1" t="n">
+      <c r="E190" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F190" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G190" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="H190" s="6" t="n">
-        <f aca="false" t="array" ref="H190:H190">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B190)*(Volume!$B$3:$B$68=E190),0), MATCH(D190,Volume!$D$2:$F$2,0))</f>
+      <c r="H190" s="7" t="n">
+        <f aca="false" t="array" ref="H190:H190">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B190)*(Volume!$B$3:$B$68=$E190),0),MATCH($D190,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="5" t="s">
+      <c r="A191" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B191" s="5" t="s">
+      <c r="B191" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C191" s="5" t="s">
+      <c r="C191" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D191" s="5" t="s">
+      <c r="D191" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E191" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F191" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G191" s="1" t="n">
+      <c r="E191" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F191" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G191" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H191" s="6" t="n">
-        <f aca="false" t="array" ref="H191:H191">INDEX(Volume!$D$3:$F$68, MATCH(1,(Volume!$A$3:$A$68=B191)*(Volume!$B$3:$B$68=E191),0), MATCH(D191,Volume!$D$2:$F$2,0))</f>
+      <c r="H191" s="7" t="n">
+        <f aca="false" t="array" ref="H191:H191">INDEX(Volume!$D$3:$F$68,MATCH(1,(Volume!$A$3:$A$68=$B191)*(Volume!$B$3:$B$68=$E191),0),MATCH($D191,Volume!$D$2:$F$2,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -5854,1383 +5858,1383 @@
   <dimension ref="A1:J69"/>
   <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="12.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="1"/>
+      <c r="G2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="0" t="n">
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="n">
         <v>169</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="2" t="n">
         <v>84.5</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="2" t="n">
         <v>42.25</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="2" t="n">
         <v>42.25</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J3" s="8" t="n">
+      <c r="J3" s="9" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="0" t="n">
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="I4" s="0" t="s">
+      <c r="I4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="8" t="n">
+      <c r="J4" s="9" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="0" t="n">
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="2" t="n">
         <v>8.5</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="2" t="n">
         <v>8.5</v>
       </c>
-      <c r="I5" s="0" t="s">
+      <c r="I5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="J5" s="9" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="0" t="n">
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="2" t="n">
         <v>8.5</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="2" t="n">
         <v>8.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="0" t="n">
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="2" t="n">
         <v>8.75</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="2" t="n">
         <v>8.75</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="0" t="n">
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="2" t="n">
         <v>5.5</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="2" t="n">
         <v>2.75</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="2" t="n">
         <v>2.75</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="0" t="n">
+      <c r="B10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="2" t="n">
         <v>2.25</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="F10" s="2" t="n">
         <v>2.25</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="0" t="n">
+      <c r="B11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="D11" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1" t="n">
+      <c r="D11" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11" s="2" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="0" t="n">
+      <c r="B12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="F12" s="1" t="n">
+      <c r="F12" s="2" t="n">
         <v>1.75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="0" t="n">
+      <c r="B13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E13" s="2" t="n">
         <f aca="false">E36</f>
         <v>2</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="F13" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="0" t="n">
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E14" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="F14" s="2" t="n">
         <v>1.75</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="0" t="n">
+      <c r="B15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D15" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="2" t="n">
         <v>1.25</v>
       </c>
-      <c r="F15" s="1" t="n">
+      <c r="F15" s="2" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="0" t="n">
+      <c r="B16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D16" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="E16" s="2" t="n">
         <v>1.25</v>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="F16" s="2" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="0" t="n">
+      <c r="B17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="F17" s="2" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="0" t="n">
+      <c r="B18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D18" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" s="2" t="n">
         <v>1.25</v>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="F18" s="2" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="0" t="n">
+      <c r="B19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="E19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="1" t="n">
+      <c r="F19" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="0" t="n">
+      <c r="B20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D20" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="E20" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="F20" s="1" t="n">
+      <c r="F20" s="2" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="0" t="n">
+      <c r="B21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="E21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="1" t="n">
+      <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="0" t="n">
+      <c r="B22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D22" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="E22" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F22" s="1" t="n">
+      <c r="F22" s="2" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="0" t="n">
+      <c r="B23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="1" t="n">
+      <c r="E23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="1" t="n">
+      <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="0" t="n">
+      <c r="B24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="1" t="n">
+      <c r="D24" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E24" s="1" t="n">
+      <c r="E24" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="F24" s="1" t="n">
+      <c r="F24" s="2" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="0" t="n">
+      <c r="C25" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="1" t="n">
+      <c r="D25" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="1" t="n">
+      <c r="E25" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F25" s="1" t="n">
+      <c r="F25" s="2" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="0" t="n">
+      <c r="B26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="1" t="n">
         <v>250</v>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D26" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="E26" s="1" t="n">
+      <c r="E26" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="F26" s="1" t="n">
+      <c r="F26" s="2" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="0" t="n">
+      <c r="B27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="D27" s="1" t="n">
+      <c r="D27" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="E27" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="F27" s="1" t="n">
+      <c r="F27" s="2" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="0" t="n">
+      <c r="B28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="D28" s="1" t="n">
+      <c r="D28" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E28" s="1" t="n">
+      <c r="E28" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="F28" s="1" t="n">
+      <c r="F28" s="2" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B29" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="0" t="n">
+      <c r="B29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D29" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="E29" s="1" t="n">
+      <c r="E29" s="2" t="n">
         <v>2.25</v>
       </c>
-      <c r="F29" s="1" t="n">
+      <c r="F29" s="2" t="n">
         <v>2.25</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="0" t="n">
+      <c r="B30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="D30" s="1" t="n">
+      <c r="D30" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E30" s="1" t="n">
+      <c r="E30" s="2" t="n">
         <v>8.5</v>
       </c>
-      <c r="F30" s="1" t="n">
+      <c r="F30" s="2" t="n">
         <v>8.5</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="0" t="n">
+      <c r="B31" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D31" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="E31" s="2" t="n">
         <v>5.5</v>
       </c>
-      <c r="F31" s="1" t="n">
+      <c r="F31" s="2" t="n">
         <v>5.5</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" s="0" t="n">
+      <c r="B32" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D32" s="1" t="n">
+      <c r="D32" s="2" t="n">
         <v>5.5</v>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="E32" s="2" t="n">
         <v>2.75</v>
       </c>
-      <c r="F32" s="1" t="n">
+      <c r="F32" s="2" t="n">
         <v>2.75</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C33" s="0" t="n">
+      <c r="B33" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D33" s="2" t="n">
         <v>7.5</v>
       </c>
-      <c r="E33" s="1" t="n">
+      <c r="E33" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="F33" s="1" t="n">
+      <c r="F33" s="2" t="n">
         <v>3.75</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="0" t="n">
+      <c r="B34" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D34" s="1" t="n">
+      <c r="D34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E34" s="1" t="n">
+      <c r="E34" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F34" s="1" t="n">
+      <c r="F34" s="2" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B35" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D35" s="1" t="n">
+      <c r="B35" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D35" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="E35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="1" t="n">
+      <c r="F35" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B36" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" s="0" t="n">
+      <c r="B36" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D36" s="1" t="n">
+      <c r="D36" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E36" s="1" t="n">
+      <c r="E36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F36" s="1" t="n">
+      <c r="F36" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="0" t="n">
+      <c r="B37" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D37" s="1" t="n">
+      <c r="D37" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E37" s="1" t="n">
+      <c r="E37" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="F37" s="1" t="n">
+      <c r="F37" s="2" t="n">
         <v>2.5</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" s="0" t="n">
+      <c r="B38" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D38" s="1" t="n">
+      <c r="D38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E38" s="1" t="n">
+      <c r="E38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="1" t="n">
+      <c r="F38" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" s="0" t="n">
+      <c r="B39" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D39" s="1" t="n">
+      <c r="D39" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="E39" s="1" t="n">
+      <c r="E39" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="F39" s="1" t="n">
+      <c r="F39" s="2" t="n">
         <v>1.75</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" s="0" t="n">
+      <c r="B40" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D40" s="1" t="n">
+      <c r="D40" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="E40" s="1" t="n">
+      <c r="E40" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="F40" s="1" t="n">
+      <c r="F40" s="2" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" s="0" t="n">
+      <c r="B41" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D41" s="1" t="n">
+      <c r="D41" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="E41" s="1" t="n">
+      <c r="E41" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="F41" s="1" t="n">
+      <c r="F41" s="2" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C42" s="0" t="n">
+      <c r="B42" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D42" s="1" t="n">
+      <c r="D42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E42" s="1" t="n">
+      <c r="E42" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F42" s="1" t="n">
+      <c r="F42" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B43" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C43" s="0" t="n">
+      <c r="B43" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D43" s="1" t="n">
+      <c r="D43" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="E43" s="1" t="n">
+      <c r="E43" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="F43" s="1" t="n">
+      <c r="F43" s="2" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B44" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C44" s="0" t="n">
+      <c r="B44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="1" t="n">
+      <c r="D44" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="E44" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="F44" s="1" t="n">
+      <c r="F44" s="2" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C45" s="0" t="n">
+      <c r="B45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D45" s="1" t="n">
+      <c r="D45" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="1" t="n">
+      <c r="E45" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="1" t="n">
+      <c r="F45" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" s="0" t="n">
+      <c r="B46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="1" t="n">
         <v>173</v>
       </c>
-      <c r="D46" s="1" t="n">
+      <c r="D46" s="2" t="n">
         <v>86.5</v>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="E46" s="2" t="n">
         <v>43.25</v>
       </c>
-      <c r="F46" s="1" t="n">
+      <c r="F46" s="2" t="n">
         <v>43.25</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B47" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" s="0" t="n">
+      <c r="B47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47" s="1" t="n">
         <v>145</v>
       </c>
-      <c r="D47" s="1" t="n">
+      <c r="D47" s="2" t="n">
         <v>72.5</v>
       </c>
-      <c r="E47" s="1" t="n">
+      <c r="E47" s="2" t="n">
         <v>36.25</v>
       </c>
-      <c r="F47" s="1" t="n">
+      <c r="F47" s="2" t="n">
         <v>36.25</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B48" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" s="0" t="n">
+      <c r="B48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="D48" s="1" t="n">
+      <c r="D48" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="E48" s="1" t="n">
+      <c r="E48" s="2" t="n">
         <v>7.25</v>
       </c>
-      <c r="F48" s="1" t="n">
+      <c r="F48" s="2" t="n">
         <v>7.25</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B49" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C49" s="0" t="n">
+      <c r="B49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="D49" s="1" t="n">
+      <c r="D49" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="E49" s="1" t="n">
+      <c r="E49" s="2" t="n">
         <v>11.25</v>
       </c>
-      <c r="F49" s="1" t="n">
+      <c r="F49" s="2" t="n">
         <v>11.25</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B50" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50" s="0" t="n">
+      <c r="B50" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="D50" s="1" t="n">
+      <c r="D50" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E50" s="1" t="n">
+      <c r="E50" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="F50" s="1" t="n">
+      <c r="F50" s="2" t="n">
         <v>4.5</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B51" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C51" s="0" t="n">
+      <c r="B51" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D51" s="1" t="n">
+      <c r="D51" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="E51" s="1" t="n">
+      <c r="E51" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="F51" s="1" t="n">
+      <c r="F51" s="2" t="n">
         <v>1.75</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B52" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C52" s="0" t="n">
+      <c r="B52" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C52" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D52" s="1" t="n">
+      <c r="D52" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E52" s="1" t="n">
+      <c r="E52" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="F52" s="1" t="n">
+      <c r="F52" s="2" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B53" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C53" s="0" t="n">
+      <c r="B53" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C53" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D53" s="1" t="n">
+      <c r="D53" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E53" s="1" t="n">
+      <c r="E53" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="F53" s="1" t="n">
+      <c r="F53" s="2" t="n">
         <v>2.5</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B54" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" s="0" t="n">
+      <c r="B54" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C54" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D54" s="1" t="n">
+      <c r="D54" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="E54" s="1" t="n">
+      <c r="E54" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="F54" s="1" t="n">
+      <c r="F54" s="2" t="n">
         <v>1.75</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B55" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C55" s="0" t="n">
+      <c r="B55" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C55" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D55" s="1" t="n">
+      <c r="D55" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="E55" s="1" t="n">
+      <c r="E55" s="2" t="n">
         <v>1.25</v>
       </c>
-      <c r="F55" s="1" t="n">
+      <c r="F55" s="2" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B56" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C56" s="0" t="n">
+      <c r="B56" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C56" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D56" s="1" t="n">
+      <c r="D56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E56" s="1" t="n">
+      <c r="E56" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F56" s="1" t="n">
+      <c r="F56" s="2" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B57" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C57" s="0" t="n">
+      <c r="B57" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C57" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D57" s="1" t="n">
+      <c r="D57" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="E57" s="1" t="n">
+      <c r="E57" s="2" t="n">
         <v>2.25</v>
       </c>
-      <c r="F57" s="1" t="n">
+      <c r="F57" s="2" t="n">
         <v>2.25</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B58" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C58" s="0" t="n">
+      <c r="B58" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C58" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D58" s="1" t="n">
+      <c r="D58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E58" s="1" t="n">
+      <c r="E58" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F58" s="1" t="n">
+      <c r="F58" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B59" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C59" s="0" t="n">
+      <c r="B59" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C59" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D59" s="1" t="n">
+      <c r="D59" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E59" s="1" t="n">
+      <c r="E59" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F59" s="1" t="n">
+      <c r="F59" s="2" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C60" s="0" t="n">
+      <c r="C60" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D60" s="1" t="n">
+      <c r="D60" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E60" s="1" t="n">
+      <c r="E60" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="1" t="n">
+      <c r="F60" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B61" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C61" s="0" t="n">
+      <c r="B61" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C61" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D61" s="1" t="n">
+      <c r="D61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E61" s="1" t="n">
+      <c r="E61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F61" s="1" t="n">
+      <c r="F61" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B62" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C62" s="0" t="n">
+      <c r="B62" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D62" s="1" t="n">
+      <c r="D62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E62" s="1" t="n">
+      <c r="E62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F62" s="1" t="n">
+      <c r="F62" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B63" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C63" s="0" t="n">
+      <c r="B63" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C63" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D63" s="1" t="n">
+      <c r="D63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E63" s="1" t="n">
+      <c r="E63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F63" s="1" t="n">
+      <c r="F63" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B64" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C64" s="0" t="n">
+      <c r="B64" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C64" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D64" s="1" t="n">
+      <c r="D64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E64" s="1" t="n">
+      <c r="E64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F64" s="1" t="n">
+      <c r="F64" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B65" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C65" s="0" t="n">
+      <c r="B65" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C65" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D65" s="1" t="n">
+      <c r="D65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E65" s="1" t="n">
+      <c r="E65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F65" s="1" t="n">
+      <c r="F65" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B66" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C66" s="0" t="n">
+      <c r="B66" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C66" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D66" s="1" t="n">
+      <c r="D66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E66" s="1" t="n">
+      <c r="E66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F66" s="1" t="n">
+      <c r="F66" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B67" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C67" s="0" t="n">
+      <c r="B67" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C67" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D67" s="1" t="n">
+      <c r="D67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E67" s="1" t="n">
+      <c r="E67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F67" s="1" t="n">
+      <c r="F67" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B68" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C68" s="0" t="n">
+      <c r="B68" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C68" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D68" s="1" t="n">
+      <c r="D68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E68" s="1" t="n">
+      <c r="E68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F68" s="1" t="n">
+      <c r="F68" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J69" s="9"/>
+      <c r="J69" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:F68"/>
